--- a/ProductBacklog_group28.xlsx
+++ b/ProductBacklog_group28.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andyf\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4303497-ACCF-4DEE-9E74-0CAD2886FCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="3790" yWindow="580" windowWidth="16550" windowHeight="13090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Story ID</t>
   </si>
@@ -43,12 +52,6 @@
     <t>Date finished (or planned)</t>
   </si>
   <si>
-    <t>This is an example.
-As a &lt;&gt;
-I want &lt;&gt;
-So that &lt;&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">This is an example.
 This is a new line
 1. List 1
@@ -56,22 +59,56 @@
 3. List 3
 </t>
   </si>
+  <si>
+    <t>This is an example.
+As a &lt;&gt;
+I want &lt;&gt;
+So that &lt;&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CV upload</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>As a &lt;TA&gt;
+I want &lt;to upload my CV in PDF&gt;
+So that &lt;Module Organizers can assign me with proper work&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>high</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -79,7 +116,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -89,7 +126,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -103,39 +146,42 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -325,29 +371,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="9.14"/>
-    <col customWidth="1" min="2" max="2" width="16.71"/>
-    <col customWidth="1" min="3" max="3" width="36.0"/>
-    <col customWidth="1" min="4" max="4" width="9.14"/>
-    <col customWidth="1" min="5" max="5" width="28.29"/>
-    <col customWidth="1" min="6" max="7" width="19.86"/>
-    <col customWidth="1" min="8" max="8" width="17.14"/>
-    <col customWidth="1" min="9" max="9" width="24.86"/>
-    <col customWidth="1" min="10" max="10" width="26.29"/>
-    <col customWidth="1" min="11" max="26" width="8.86"/>
+    <col min="1" max="1" width="9.08984375" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" customWidth="1"/>
+    <col min="5" max="5" width="28.26953125" customWidth="1"/>
+    <col min="6" max="7" width="19.81640625" customWidth="1"/>
+    <col min="8" max="8" width="17.08984375" customWidth="1"/>
+    <col min="9" max="9" width="24.81640625" customWidth="1"/>
+    <col min="10" max="10" width="26.26953125" customWidth="1"/>
+    <col min="11" max="26" width="8.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -379,35 +425,45 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -419,7 +475,7 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -431,7 +487,7 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -443,7 +499,7 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -455,7 +511,7 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -467,7 +523,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -479,7 +535,7 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -491,7 +547,7 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -503,7 +559,7 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -515,7 +571,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -527,7 +583,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -539,7 +595,7 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -551,7 +607,7 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -563,7 +619,7 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -575,7 +631,7 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -587,7 +643,7 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -599,7 +655,7 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -611,7 +667,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -623,7 +679,7 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -635,7 +691,7 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -647,7 +703,7 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -659,7 +715,7 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -671,7 +727,7 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -683,7 +739,7 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -695,7 +751,7 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -707,7 +763,7 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -719,7 +775,7 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -731,7 +787,7 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -743,7 +799,7 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -755,7 +811,7 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -767,7 +823,7 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -779,7 +835,7 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -791,7 +847,7 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -803,7 +859,7 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -815,7 +871,7 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -827,7 +883,7 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -839,7 +895,7 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -851,7 +907,7 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -863,7 +919,7 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -875,7 +931,7 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -887,7 +943,7 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -899,7 +955,7 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -911,7 +967,7 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -923,7 +979,7 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -935,7 +991,7 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -947,7 +1003,7 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -959,7 +1015,7 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -971,7 +1027,7 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -983,7 +1039,7 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -995,7 +1051,7 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -1007,7 +1063,7 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -1019,7 +1075,7 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -1031,7 +1087,7 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -1043,7 +1099,7 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -1055,7 +1111,7 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -1067,7 +1123,7 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -1079,7 +1135,7 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -1091,7 +1147,7 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -1103,7 +1159,7 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -1115,7 +1171,7 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -1127,7 +1183,7 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -1139,7 +1195,7 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -1151,7 +1207,7 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -1163,7 +1219,7 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -1175,7 +1231,7 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -1187,7 +1243,7 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -1199,7 +1255,7 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -1211,7 +1267,7 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -1223,7 +1279,7 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -1235,7 +1291,7 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -1247,7 +1303,7 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -1259,7 +1315,7 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -1271,7 +1327,7 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -1283,7 +1339,7 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -1295,7 +1351,7 @@
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -1307,7 +1363,7 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -1319,7 +1375,7 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -1331,7 +1387,7 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -1343,7 +1399,7 @@
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -1355,7 +1411,7 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -1367,7 +1423,7 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -1379,7 +1435,7 @@
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -1391,7 +1447,7 @@
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -1403,7 +1459,7 @@
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -1415,7 +1471,7 @@
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -1427,7 +1483,7 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -1439,7 +1495,7 @@
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -1451,7 +1507,7 @@
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -1463,7 +1519,7 @@
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -1475,7 +1531,7 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -1487,7 +1543,7 @@
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -1499,7 +1555,7 @@
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -1511,7 +1567,7 @@
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -1523,7 +1579,7 @@
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -1535,7 +1591,7 @@
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -1547,7 +1603,7 @@
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -1559,7 +1615,7 @@
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -1571,7 +1627,7 @@
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -1583,7 +1639,7 @@
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -1595,7 +1651,7 @@
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -1607,7 +1663,7 @@
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -1619,7 +1675,7 @@
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -1631,7 +1687,7 @@
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -1643,7 +1699,7 @@
       <c r="I106" s="2"/>
       <c r="J106" s="2"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -1655,7 +1711,7 @@
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -1667,7 +1723,7 @@
       <c r="I108" s="2"/>
       <c r="J108" s="2"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -1679,7 +1735,7 @@
       <c r="I109" s="2"/>
       <c r="J109" s="2"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -1691,7 +1747,7 @@
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -1703,7 +1759,7 @@
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -1715,7 +1771,7 @@
       <c r="I112" s="2"/>
       <c r="J112" s="2"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -1727,7 +1783,7 @@
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -1739,7 +1795,7 @@
       <c r="I114" s="2"/>
       <c r="J114" s="2"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -1751,7 +1807,7 @@
       <c r="I115" s="2"/>
       <c r="J115" s="2"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -1763,7 +1819,7 @@
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -1775,7 +1831,7 @@
       <c r="I117" s="2"/>
       <c r="J117" s="2"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -1787,7 +1843,7 @@
       <c r="I118" s="2"/>
       <c r="J118" s="2"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -1799,7 +1855,7 @@
       <c r="I119" s="2"/>
       <c r="J119" s="2"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -1811,7 +1867,7 @@
       <c r="I120" s="2"/>
       <c r="J120" s="2"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -1823,7 +1879,7 @@
       <c r="I121" s="2"/>
       <c r="J121" s="2"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -1835,7 +1891,7 @@
       <c r="I122" s="2"/>
       <c r="J122" s="2"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -1847,7 +1903,7 @@
       <c r="I123" s="2"/>
       <c r="J123" s="2"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -1859,7 +1915,7 @@
       <c r="I124" s="2"/>
       <c r="J124" s="2"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -1871,7 +1927,7 @@
       <c r="I125" s="2"/>
       <c r="J125" s="2"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -1883,7 +1939,7 @@
       <c r="I126" s="2"/>
       <c r="J126" s="2"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -1895,7 +1951,7 @@
       <c r="I127" s="2"/>
       <c r="J127" s="2"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -1907,7 +1963,7 @@
       <c r="I128" s="2"/>
       <c r="J128" s="2"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -1919,7 +1975,7 @@
       <c r="I129" s="2"/>
       <c r="J129" s="2"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -1931,7 +1987,7 @@
       <c r="I130" s="2"/>
       <c r="J130" s="2"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -1943,7 +1999,7 @@
       <c r="I131" s="2"/>
       <c r="J131" s="2"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -1955,7 +2011,7 @@
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -1967,7 +2023,7 @@
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -1979,7 +2035,7 @@
       <c r="I134" s="2"/>
       <c r="J134" s="2"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -1991,7 +2047,7 @@
       <c r="I135" s="2"/>
       <c r="J135" s="2"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -2003,7 +2059,7 @@
       <c r="I136" s="2"/>
       <c r="J136" s="2"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -2015,7 +2071,7 @@
       <c r="I137" s="2"/>
       <c r="J137" s="2"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -2027,7 +2083,7 @@
       <c r="I138" s="2"/>
       <c r="J138" s="2"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -2039,7 +2095,7 @@
       <c r="I139" s="2"/>
       <c r="J139" s="2"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -2051,7 +2107,7 @@
       <c r="I140" s="2"/>
       <c r="J140" s="2"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -2063,7 +2119,7 @@
       <c r="I141" s="2"/>
       <c r="J141" s="2"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -2075,7 +2131,7 @@
       <c r="I142" s="2"/>
       <c r="J142" s="2"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -2087,7 +2143,7 @@
       <c r="I143" s="2"/>
       <c r="J143" s="2"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -2099,7 +2155,7 @@
       <c r="I144" s="2"/>
       <c r="J144" s="2"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -2111,7 +2167,7 @@
       <c r="I145" s="2"/>
       <c r="J145" s="2"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -2123,7 +2179,7 @@
       <c r="I146" s="2"/>
       <c r="J146" s="2"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -2135,7 +2191,7 @@
       <c r="I147" s="2"/>
       <c r="J147" s="2"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -2147,7 +2203,7 @@
       <c r="I148" s="2"/>
       <c r="J148" s="2"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -2159,7 +2215,7 @@
       <c r="I149" s="2"/>
       <c r="J149" s="2"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -2171,7 +2227,7 @@
       <c r="I150" s="2"/>
       <c r="J150" s="2"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -2183,7 +2239,7 @@
       <c r="I151" s="2"/>
       <c r="J151" s="2"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -2195,7 +2251,7 @@
       <c r="I152" s="2"/>
       <c r="J152" s="2"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -2207,7 +2263,7 @@
       <c r="I153" s="2"/>
       <c r="J153" s="2"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -2219,7 +2275,7 @@
       <c r="I154" s="2"/>
       <c r="J154" s="2"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -2231,7 +2287,7 @@
       <c r="I155" s="2"/>
       <c r="J155" s="2"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -2243,7 +2299,7 @@
       <c r="I156" s="2"/>
       <c r="J156" s="2"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -2255,7 +2311,7 @@
       <c r="I157" s="2"/>
       <c r="J157" s="2"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -2267,7 +2323,7 @@
       <c r="I158" s="2"/>
       <c r="J158" s="2"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -2279,7 +2335,7 @@
       <c r="I159" s="2"/>
       <c r="J159" s="2"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -2291,7 +2347,7 @@
       <c r="I160" s="2"/>
       <c r="J160" s="2"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -2303,7 +2359,7 @@
       <c r="I161" s="2"/>
       <c r="J161" s="2"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -2315,7 +2371,7 @@
       <c r="I162" s="2"/>
       <c r="J162" s="2"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -2327,7 +2383,7 @@
       <c r="I163" s="2"/>
       <c r="J163" s="2"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -2339,7 +2395,7 @@
       <c r="I164" s="2"/>
       <c r="J164" s="2"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -2351,7 +2407,7 @@
       <c r="I165" s="2"/>
       <c r="J165" s="2"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -2363,7 +2419,7 @@
       <c r="I166" s="2"/>
       <c r="J166" s="2"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -2375,7 +2431,7 @@
       <c r="I167" s="2"/>
       <c r="J167" s="2"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -2387,7 +2443,7 @@
       <c r="I168" s="2"/>
       <c r="J168" s="2"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -2399,7 +2455,7 @@
       <c r="I169" s="2"/>
       <c r="J169" s="2"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -2411,7 +2467,7 @@
       <c r="I170" s="2"/>
       <c r="J170" s="2"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -2423,7 +2479,7 @@
       <c r="I171" s="2"/>
       <c r="J171" s="2"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -2435,7 +2491,7 @@
       <c r="I172" s="2"/>
       <c r="J172" s="2"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -2447,7 +2503,7 @@
       <c r="I173" s="2"/>
       <c r="J173" s="2"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -2459,7 +2515,7 @@
       <c r="I174" s="2"/>
       <c r="J174" s="2"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -2471,7 +2527,7 @@
       <c r="I175" s="2"/>
       <c r="J175" s="2"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -2483,7 +2539,7 @@
       <c r="I176" s="2"/>
       <c r="J176" s="2"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -2495,7 +2551,7 @@
       <c r="I177" s="2"/>
       <c r="J177" s="2"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -2507,7 +2563,7 @@
       <c r="I178" s="2"/>
       <c r="J178" s="2"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -2519,7 +2575,7 @@
       <c r="I179" s="2"/>
       <c r="J179" s="2"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -2531,7 +2587,7 @@
       <c r="I180" s="2"/>
       <c r="J180" s="2"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -2543,7 +2599,7 @@
       <c r="I181" s="2"/>
       <c r="J181" s="2"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -2555,7 +2611,7 @@
       <c r="I182" s="2"/>
       <c r="J182" s="2"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -2567,7 +2623,7 @@
       <c r="I183" s="2"/>
       <c r="J183" s="2"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -2579,7 +2635,7 @@
       <c r="I184" s="2"/>
       <c r="J184" s="2"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -2591,7 +2647,7 @@
       <c r="I185" s="2"/>
       <c r="J185" s="2"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -2603,7 +2659,7 @@
       <c r="I186" s="2"/>
       <c r="J186" s="2"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -2615,7 +2671,7 @@
       <c r="I187" s="2"/>
       <c r="J187" s="2"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -2627,7 +2683,7 @@
       <c r="I188" s="2"/>
       <c r="J188" s="2"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -2639,7 +2695,7 @@
       <c r="I189" s="2"/>
       <c r="J189" s="2"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -2651,7 +2707,7 @@
       <c r="I190" s="2"/>
       <c r="J190" s="2"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -2663,7 +2719,7 @@
       <c r="I191" s="2"/>
       <c r="J191" s="2"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -2675,7 +2731,7 @@
       <c r="I192" s="2"/>
       <c r="J192" s="2"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -2687,7 +2743,7 @@
       <c r="I193" s="2"/>
       <c r="J193" s="2"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -2699,7 +2755,7 @@
       <c r="I194" s="2"/>
       <c r="J194" s="2"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -2711,7 +2767,7 @@
       <c r="I195" s="2"/>
       <c r="J195" s="2"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -2723,7 +2779,7 @@
       <c r="I196" s="2"/>
       <c r="J196" s="2"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -2735,7 +2791,7 @@
       <c r="I197" s="2"/>
       <c r="J197" s="2"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -2747,7 +2803,7 @@
       <c r="I198" s="2"/>
       <c r="J198" s="2"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -2759,7 +2815,7 @@
       <c r="I199" s="2"/>
       <c r="J199" s="2"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -2771,7 +2827,7 @@
       <c r="I200" s="2"/>
       <c r="J200" s="2"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -2783,7 +2839,7 @@
       <c r="I201" s="2"/>
       <c r="J201" s="2"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -2795,7 +2851,7 @@
       <c r="I202" s="2"/>
       <c r="J202" s="2"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -2807,7 +2863,7 @@
       <c r="I203" s="2"/>
       <c r="J203" s="2"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -2819,7 +2875,7 @@
       <c r="I204" s="2"/>
       <c r="J204" s="2"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -2831,7 +2887,7 @@
       <c r="I205" s="2"/>
       <c r="J205" s="2"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -2843,7 +2899,7 @@
       <c r="I206" s="2"/>
       <c r="J206" s="2"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -2855,7 +2911,7 @@
       <c r="I207" s="2"/>
       <c r="J207" s="2"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -2867,7 +2923,7 @@
       <c r="I208" s="2"/>
       <c r="J208" s="2"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -2879,7 +2935,7 @@
       <c r="I209" s="2"/>
       <c r="J209" s="2"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -2891,7 +2947,7 @@
       <c r="I210" s="2"/>
       <c r="J210" s="2"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -2903,7 +2959,7 @@
       <c r="I211" s="2"/>
       <c r="J211" s="2"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -2915,7 +2971,7 @@
       <c r="I212" s="2"/>
       <c r="J212" s="2"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -2927,7 +2983,7 @@
       <c r="I213" s="2"/>
       <c r="J213" s="2"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -2939,7 +2995,7 @@
       <c r="I214" s="2"/>
       <c r="J214" s="2"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -2951,7 +3007,7 @@
       <c r="I215" s="2"/>
       <c r="J215" s="2"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -2963,7 +3019,7 @@
       <c r="I216" s="2"/>
       <c r="J216" s="2"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -2975,7 +3031,7 @@
       <c r="I217" s="2"/>
       <c r="J217" s="2"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -2987,7 +3043,7 @@
       <c r="I218" s="2"/>
       <c r="J218" s="2"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -2999,7 +3055,7 @@
       <c r="I219" s="2"/>
       <c r="J219" s="2"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -3011,7 +3067,7 @@
       <c r="I220" s="2"/>
       <c r="J220" s="2"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row r="221" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -3023,7 +3079,7 @@
       <c r="I221" s="2"/>
       <c r="J221" s="2"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row r="222" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -3035,7 +3091,7 @@
       <c r="I222" s="2"/>
       <c r="J222" s="2"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row r="223" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -3047,7 +3103,7 @@
       <c r="I223" s="2"/>
       <c r="J223" s="2"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row r="224" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -3059,7 +3115,7 @@
       <c r="I224" s="2"/>
       <c r="J224" s="2"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row r="225" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -3071,7 +3127,7 @@
       <c r="I225" s="2"/>
       <c r="J225" s="2"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row r="226" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -3083,7 +3139,7 @@
       <c r="I226" s="2"/>
       <c r="J226" s="2"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row r="227" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -3095,7 +3151,7 @@
       <c r="I227" s="2"/>
       <c r="J227" s="2"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row r="228" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -3107,7 +3163,7 @@
       <c r="I228" s="2"/>
       <c r="J228" s="2"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row r="229" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -3119,7 +3175,7 @@
       <c r="I229" s="2"/>
       <c r="J229" s="2"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row r="230" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -3131,7 +3187,7 @@
       <c r="I230" s="2"/>
       <c r="J230" s="2"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row r="231" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -3143,7 +3199,7 @@
       <c r="I231" s="2"/>
       <c r="J231" s="2"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row r="232" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -3155,7 +3211,7 @@
       <c r="I232" s="2"/>
       <c r="J232" s="2"/>
     </row>
-    <row r="233" ht="15.75" customHeight="1">
+    <row r="233" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -3167,7 +3223,7 @@
       <c r="I233" s="2"/>
       <c r="J233" s="2"/>
     </row>
-    <row r="234" ht="15.75" customHeight="1">
+    <row r="234" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -3179,7 +3235,7 @@
       <c r="I234" s="2"/>
       <c r="J234" s="2"/>
     </row>
-    <row r="235" ht="15.75" customHeight="1">
+    <row r="235" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -3191,7 +3247,7 @@
       <c r="I235" s="2"/>
       <c r="J235" s="2"/>
     </row>
-    <row r="236" ht="15.75" customHeight="1">
+    <row r="236" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -3203,7 +3259,7 @@
       <c r="I236" s="2"/>
       <c r="J236" s="2"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1">
+    <row r="237" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -3215,7 +3271,7 @@
       <c r="I237" s="2"/>
       <c r="J237" s="2"/>
     </row>
-    <row r="238" ht="15.75" customHeight="1">
+    <row r="238" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -3227,7 +3283,7 @@
       <c r="I238" s="2"/>
       <c r="J238" s="2"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1">
+    <row r="239" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -3239,7 +3295,7 @@
       <c r="I239" s="2"/>
       <c r="J239" s="2"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1">
+    <row r="240" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -3251,7 +3307,7 @@
       <c r="I240" s="2"/>
       <c r="J240" s="2"/>
     </row>
-    <row r="241" ht="15.75" customHeight="1">
+    <row r="241" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -3263,7 +3319,7 @@
       <c r="I241" s="2"/>
       <c r="J241" s="2"/>
     </row>
-    <row r="242" ht="15.75" customHeight="1">
+    <row r="242" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -3275,7 +3331,7 @@
       <c r="I242" s="2"/>
       <c r="J242" s="2"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1">
+    <row r="243" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -3287,7 +3343,7 @@
       <c r="I243" s="2"/>
       <c r="J243" s="2"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1">
+    <row r="244" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -3299,7 +3355,7 @@
       <c r="I244" s="2"/>
       <c r="J244" s="2"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1">
+    <row r="245" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -3311,7 +3367,7 @@
       <c r="I245" s="2"/>
       <c r="J245" s="2"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1">
+    <row r="246" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -3323,7 +3379,7 @@
       <c r="I246" s="2"/>
       <c r="J246" s="2"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1">
+    <row r="247" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -3335,7 +3391,7 @@
       <c r="I247" s="2"/>
       <c r="J247" s="2"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1">
+    <row r="248" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -3347,7 +3403,7 @@
       <c r="I248" s="2"/>
       <c r="J248" s="2"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
+    <row r="249" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -3359,7 +3415,7 @@
       <c r="I249" s="2"/>
       <c r="J249" s="2"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row r="250" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -3371,7 +3427,7 @@
       <c r="I250" s="2"/>
       <c r="J250" s="2"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1">
+    <row r="251" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -3383,7 +3439,7 @@
       <c r="I251" s="2"/>
       <c r="J251" s="2"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1">
+    <row r="252" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -3395,7 +3451,7 @@
       <c r="I252" s="2"/>
       <c r="J252" s="2"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1">
+    <row r="253" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -3407,7 +3463,7 @@
       <c r="I253" s="2"/>
       <c r="J253" s="2"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1">
+    <row r="254" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -3419,7 +3475,7 @@
       <c r="I254" s="2"/>
       <c r="J254" s="2"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1">
+    <row r="255" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -3431,7 +3487,7 @@
       <c r="I255" s="2"/>
       <c r="J255" s="2"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1">
+    <row r="256" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -3443,7 +3499,7 @@
       <c r="I256" s="2"/>
       <c r="J256" s="2"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1">
+    <row r="257" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -3455,7 +3511,7 @@
       <c r="I257" s="2"/>
       <c r="J257" s="2"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row r="258" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -3467,7 +3523,7 @@
       <c r="I258" s="2"/>
       <c r="J258" s="2"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -3479,7 +3535,7 @@
       <c r="I259" s="2"/>
       <c r="J259" s="2"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1">
+    <row r="260" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -3491,7 +3547,7 @@
       <c r="I260" s="2"/>
       <c r="J260" s="2"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1">
+    <row r="261" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -3503,7 +3559,7 @@
       <c r="I261" s="2"/>
       <c r="J261" s="2"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1">
+    <row r="262" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -3515,7 +3571,7 @@
       <c r="I262" s="2"/>
       <c r="J262" s="2"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
+    <row r="263" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -3527,7 +3583,7 @@
       <c r="I263" s="2"/>
       <c r="J263" s="2"/>
     </row>
-    <row r="264" ht="15.75" customHeight="1">
+    <row r="264" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -3539,7 +3595,7 @@
       <c r="I264" s="2"/>
       <c r="J264" s="2"/>
     </row>
-    <row r="265" ht="15.75" customHeight="1">
+    <row r="265" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -3551,7 +3607,7 @@
       <c r="I265" s="2"/>
       <c r="J265" s="2"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1">
+    <row r="266" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -3563,7 +3619,7 @@
       <c r="I266" s="2"/>
       <c r="J266" s="2"/>
     </row>
-    <row r="267" ht="15.75" customHeight="1">
+    <row r="267" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -3575,7 +3631,7 @@
       <c r="I267" s="2"/>
       <c r="J267" s="2"/>
     </row>
-    <row r="268" ht="15.75" customHeight="1">
+    <row r="268" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -3587,7 +3643,7 @@
       <c r="I268" s="2"/>
       <c r="J268" s="2"/>
     </row>
-    <row r="269" ht="15.75" customHeight="1">
+    <row r="269" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -3599,7 +3655,7 @@
       <c r="I269" s="2"/>
       <c r="J269" s="2"/>
     </row>
-    <row r="270" ht="15.75" customHeight="1">
+    <row r="270" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -3611,7 +3667,7 @@
       <c r="I270" s="2"/>
       <c r="J270" s="2"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1">
+    <row r="271" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -3623,7 +3679,7 @@
       <c r="I271" s="2"/>
       <c r="J271" s="2"/>
     </row>
-    <row r="272" ht="15.75" customHeight="1">
+    <row r="272" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -3635,7 +3691,7 @@
       <c r="I272" s="2"/>
       <c r="J272" s="2"/>
     </row>
-    <row r="273" ht="15.75" customHeight="1">
+    <row r="273" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -3647,7 +3703,7 @@
       <c r="I273" s="2"/>
       <c r="J273" s="2"/>
     </row>
-    <row r="274" ht="15.75" customHeight="1">
+    <row r="274" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -3659,7 +3715,7 @@
       <c r="I274" s="2"/>
       <c r="J274" s="2"/>
     </row>
-    <row r="275" ht="15.75" customHeight="1">
+    <row r="275" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -3671,7 +3727,7 @@
       <c r="I275" s="2"/>
       <c r="J275" s="2"/>
     </row>
-    <row r="276" ht="15.75" customHeight="1">
+    <row r="276" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -3683,7 +3739,7 @@
       <c r="I276" s="2"/>
       <c r="J276" s="2"/>
     </row>
-    <row r="277" ht="15.75" customHeight="1">
+    <row r="277" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -3695,7 +3751,7 @@
       <c r="I277" s="2"/>
       <c r="J277" s="2"/>
     </row>
-    <row r="278" ht="15.75" customHeight="1">
+    <row r="278" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -3707,7 +3763,7 @@
       <c r="I278" s="2"/>
       <c r="J278" s="2"/>
     </row>
-    <row r="279" ht="15.75" customHeight="1">
+    <row r="279" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -3719,7 +3775,7 @@
       <c r="I279" s="2"/>
       <c r="J279" s="2"/>
     </row>
-    <row r="280" ht="15.75" customHeight="1">
+    <row r="280" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -3731,7 +3787,7 @@
       <c r="I280" s="2"/>
       <c r="J280" s="2"/>
     </row>
-    <row r="281" ht="15.75" customHeight="1">
+    <row r="281" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -3743,7 +3799,7 @@
       <c r="I281" s="2"/>
       <c r="J281" s="2"/>
     </row>
-    <row r="282" ht="15.75" customHeight="1">
+    <row r="282" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -3755,7 +3811,7 @@
       <c r="I282" s="2"/>
       <c r="J282" s="2"/>
     </row>
-    <row r="283" ht="15.75" customHeight="1">
+    <row r="283" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -3767,7 +3823,7 @@
       <c r="I283" s="2"/>
       <c r="J283" s="2"/>
     </row>
-    <row r="284" ht="15.75" customHeight="1">
+    <row r="284" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -3779,7 +3835,7 @@
       <c r="I284" s="2"/>
       <c r="J284" s="2"/>
     </row>
-    <row r="285" ht="15.75" customHeight="1">
+    <row r="285" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -3791,7 +3847,7 @@
       <c r="I285" s="2"/>
       <c r="J285" s="2"/>
     </row>
-    <row r="286" ht="15.75" customHeight="1">
+    <row r="286" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -3803,7 +3859,7 @@
       <c r="I286" s="2"/>
       <c r="J286" s="2"/>
     </row>
-    <row r="287" ht="15.75" customHeight="1">
+    <row r="287" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -3815,7 +3871,7 @@
       <c r="I287" s="2"/>
       <c r="J287" s="2"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1">
+    <row r="288" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -3827,7 +3883,7 @@
       <c r="I288" s="2"/>
       <c r="J288" s="2"/>
     </row>
-    <row r="289" ht="15.75" customHeight="1">
+    <row r="289" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -3839,7 +3895,7 @@
       <c r="I289" s="2"/>
       <c r="J289" s="2"/>
     </row>
-    <row r="290" ht="15.75" customHeight="1">
+    <row r="290" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -3851,7 +3907,7 @@
       <c r="I290" s="2"/>
       <c r="J290" s="2"/>
     </row>
-    <row r="291" ht="15.75" customHeight="1">
+    <row r="291" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -3863,7 +3919,7 @@
       <c r="I291" s="2"/>
       <c r="J291" s="2"/>
     </row>
-    <row r="292" ht="15.75" customHeight="1">
+    <row r="292" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -3875,7 +3931,7 @@
       <c r="I292" s="2"/>
       <c r="J292" s="2"/>
     </row>
-    <row r="293" ht="15.75" customHeight="1">
+    <row r="293" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -3887,7 +3943,7 @@
       <c r="I293" s="2"/>
       <c r="J293" s="2"/>
     </row>
-    <row r="294" ht="15.75" customHeight="1">
+    <row r="294" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -3899,7 +3955,7 @@
       <c r="I294" s="2"/>
       <c r="J294" s="2"/>
     </row>
-    <row r="295" ht="15.75" customHeight="1">
+    <row r="295" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -3911,7 +3967,7 @@
       <c r="I295" s="2"/>
       <c r="J295" s="2"/>
     </row>
-    <row r="296" ht="15.75" customHeight="1">
+    <row r="296" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -3923,7 +3979,7 @@
       <c r="I296" s="2"/>
       <c r="J296" s="2"/>
     </row>
-    <row r="297" ht="15.75" customHeight="1">
+    <row r="297" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -3935,7 +3991,7 @@
       <c r="I297" s="2"/>
       <c r="J297" s="2"/>
     </row>
-    <row r="298" ht="15.75" customHeight="1">
+    <row r="298" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -3947,7 +4003,7 @@
       <c r="I298" s="2"/>
       <c r="J298" s="2"/>
     </row>
-    <row r="299" ht="15.75" customHeight="1">
+    <row r="299" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -3959,7 +4015,7 @@
       <c r="I299" s="2"/>
       <c r="J299" s="2"/>
     </row>
-    <row r="300" ht="15.75" customHeight="1">
+    <row r="300" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -3971,7 +4027,7 @@
       <c r="I300" s="2"/>
       <c r="J300" s="2"/>
     </row>
-    <row r="301" ht="15.75" customHeight="1">
+    <row r="301" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -3983,7 +4039,7 @@
       <c r="I301" s="2"/>
       <c r="J301" s="2"/>
     </row>
-    <row r="302" ht="15.75" customHeight="1">
+    <row r="302" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
@@ -3995,7 +4051,7 @@
       <c r="I302" s="2"/>
       <c r="J302" s="2"/>
     </row>
-    <row r="303" ht="15.75" customHeight="1">
+    <row r="303" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -4007,7 +4063,7 @@
       <c r="I303" s="2"/>
       <c r="J303" s="2"/>
     </row>
-    <row r="304" ht="15.75" customHeight="1">
+    <row r="304" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -4019,7 +4075,7 @@
       <c r="I304" s="2"/>
       <c r="J304" s="2"/>
     </row>
-    <row r="305" ht="15.75" customHeight="1">
+    <row r="305" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
@@ -4031,7 +4087,7 @@
       <c r="I305" s="2"/>
       <c r="J305" s="2"/>
     </row>
-    <row r="306" ht="15.75" customHeight="1">
+    <row r="306" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
@@ -4043,7 +4099,7 @@
       <c r="I306" s="2"/>
       <c r="J306" s="2"/>
     </row>
-    <row r="307" ht="15.75" customHeight="1">
+    <row r="307" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
@@ -4055,7 +4111,7 @@
       <c r="I307" s="2"/>
       <c r="J307" s="2"/>
     </row>
-    <row r="308" ht="15.75" customHeight="1">
+    <row r="308" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
@@ -4067,7 +4123,7 @@
       <c r="I308" s="2"/>
       <c r="J308" s="2"/>
     </row>
-    <row r="309" ht="15.75" customHeight="1">
+    <row r="309" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
@@ -4079,7 +4135,7 @@
       <c r="I309" s="2"/>
       <c r="J309" s="2"/>
     </row>
-    <row r="310" ht="15.75" customHeight="1">
+    <row r="310" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
@@ -4091,7 +4147,7 @@
       <c r="I310" s="2"/>
       <c r="J310" s="2"/>
     </row>
-    <row r="311" ht="15.75" customHeight="1">
+    <row r="311" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
@@ -4103,7 +4159,7 @@
       <c r="I311" s="2"/>
       <c r="J311" s="2"/>
     </row>
-    <row r="312" ht="15.75" customHeight="1">
+    <row r="312" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -4115,7 +4171,7 @@
       <c r="I312" s="2"/>
       <c r="J312" s="2"/>
     </row>
-    <row r="313" ht="15.75" customHeight="1">
+    <row r="313" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -4127,7 +4183,7 @@
       <c r="I313" s="2"/>
       <c r="J313" s="2"/>
     </row>
-    <row r="314" ht="15.75" customHeight="1">
+    <row r="314" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
@@ -4139,7 +4195,7 @@
       <c r="I314" s="2"/>
       <c r="J314" s="2"/>
     </row>
-    <row r="315" ht="15.75" customHeight="1">
+    <row r="315" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
@@ -4151,7 +4207,7 @@
       <c r="I315" s="2"/>
       <c r="J315" s="2"/>
     </row>
-    <row r="316" ht="15.75" customHeight="1">
+    <row r="316" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
@@ -4163,7 +4219,7 @@
       <c r="I316" s="2"/>
       <c r="J316" s="2"/>
     </row>
-    <row r="317" ht="15.75" customHeight="1">
+    <row r="317" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
@@ -4175,7 +4231,7 @@
       <c r="I317" s="2"/>
       <c r="J317" s="2"/>
     </row>
-    <row r="318" ht="15.75" customHeight="1">
+    <row r="318" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
@@ -4187,7 +4243,7 @@
       <c r="I318" s="2"/>
       <c r="J318" s="2"/>
     </row>
-    <row r="319" ht="15.75" customHeight="1">
+    <row r="319" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
@@ -4199,7 +4255,7 @@
       <c r="I319" s="2"/>
       <c r="J319" s="2"/>
     </row>
-    <row r="320" ht="15.75" customHeight="1">
+    <row r="320" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
@@ -4211,7 +4267,7 @@
       <c r="I320" s="2"/>
       <c r="J320" s="2"/>
     </row>
-    <row r="321" ht="15.75" customHeight="1">
+    <row r="321" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
@@ -4223,7 +4279,7 @@
       <c r="I321" s="2"/>
       <c r="J321" s="2"/>
     </row>
-    <row r="322" ht="15.75" customHeight="1">
+    <row r="322" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="2"/>
@@ -4235,7 +4291,7 @@
       <c r="I322" s="2"/>
       <c r="J322" s="2"/>
     </row>
-    <row r="323" ht="15.75" customHeight="1">
+    <row r="323" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="2"/>
@@ -4247,7 +4303,7 @@
       <c r="I323" s="2"/>
       <c r="J323" s="2"/>
     </row>
-    <row r="324" ht="15.75" customHeight="1">
+    <row r="324" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="2"/>
@@ -4259,7 +4315,7 @@
       <c r="I324" s="2"/>
       <c r="J324" s="2"/>
     </row>
-    <row r="325" ht="15.75" customHeight="1">
+    <row r="325" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="2"/>
@@ -4271,7 +4327,7 @@
       <c r="I325" s="2"/>
       <c r="J325" s="2"/>
     </row>
-    <row r="326" ht="15.75" customHeight="1">
+    <row r="326" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="2"/>
@@ -4283,7 +4339,7 @@
       <c r="I326" s="2"/>
       <c r="J326" s="2"/>
     </row>
-    <row r="327" ht="15.75" customHeight="1">
+    <row r="327" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="2"/>
@@ -4295,7 +4351,7 @@
       <c r="I327" s="2"/>
       <c r="J327" s="2"/>
     </row>
-    <row r="328" ht="15.75" customHeight="1">
+    <row r="328" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="2"/>
@@ -4307,7 +4363,7 @@
       <c r="I328" s="2"/>
       <c r="J328" s="2"/>
     </row>
-    <row r="329" ht="15.75" customHeight="1">
+    <row r="329" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="2"/>
@@ -4319,7 +4375,7 @@
       <c r="I329" s="2"/>
       <c r="J329" s="2"/>
     </row>
-    <row r="330" ht="15.75" customHeight="1">
+    <row r="330" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="2"/>
@@ -4331,7 +4387,7 @@
       <c r="I330" s="2"/>
       <c r="J330" s="2"/>
     </row>
-    <row r="331" ht="15.75" customHeight="1">
+    <row r="331" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
@@ -4343,7 +4399,7 @@
       <c r="I331" s="2"/>
       <c r="J331" s="2"/>
     </row>
-    <row r="332" ht="15.75" customHeight="1">
+    <row r="332" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="2"/>
@@ -4355,7 +4411,7 @@
       <c r="I332" s="2"/>
       <c r="J332" s="2"/>
     </row>
-    <row r="333" ht="15.75" customHeight="1">
+    <row r="333" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="2"/>
@@ -4367,7 +4423,7 @@
       <c r="I333" s="2"/>
       <c r="J333" s="2"/>
     </row>
-    <row r="334" ht="15.75" customHeight="1">
+    <row r="334" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="2"/>
@@ -4379,7 +4435,7 @@
       <c r="I334" s="2"/>
       <c r="J334" s="2"/>
     </row>
-    <row r="335" ht="15.75" customHeight="1">
+    <row r="335" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="2"/>
@@ -4391,7 +4447,7 @@
       <c r="I335" s="2"/>
       <c r="J335" s="2"/>
     </row>
-    <row r="336" ht="15.75" customHeight="1">
+    <row r="336" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="2"/>
@@ -4403,7 +4459,7 @@
       <c r="I336" s="2"/>
       <c r="J336" s="2"/>
     </row>
-    <row r="337" ht="15.75" customHeight="1">
+    <row r="337" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="2"/>
@@ -4415,7 +4471,7 @@
       <c r="I337" s="2"/>
       <c r="J337" s="2"/>
     </row>
-    <row r="338" ht="15.75" customHeight="1">
+    <row r="338" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="2"/>
@@ -4427,7 +4483,7 @@
       <c r="I338" s="2"/>
       <c r="J338" s="2"/>
     </row>
-    <row r="339" ht="15.75" customHeight="1">
+    <row r="339" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="2"/>
@@ -4439,7 +4495,7 @@
       <c r="I339" s="2"/>
       <c r="J339" s="2"/>
     </row>
-    <row r="340" ht="15.75" customHeight="1">
+    <row r="340" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="2"/>
@@ -4451,7 +4507,7 @@
       <c r="I340" s="2"/>
       <c r="J340" s="2"/>
     </row>
-    <row r="341" ht="15.75" customHeight="1">
+    <row r="341" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="2"/>
@@ -4463,7 +4519,7 @@
       <c r="I341" s="2"/>
       <c r="J341" s="2"/>
     </row>
-    <row r="342" ht="15.75" customHeight="1">
+    <row r="342" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="2"/>
@@ -4475,7 +4531,7 @@
       <c r="I342" s="2"/>
       <c r="J342" s="2"/>
     </row>
-    <row r="343" ht="15.75" customHeight="1">
+    <row r="343" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="2"/>
@@ -4487,7 +4543,7 @@
       <c r="I343" s="2"/>
       <c r="J343" s="2"/>
     </row>
-    <row r="344" ht="15.75" customHeight="1">
+    <row r="344" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="2"/>
@@ -4499,7 +4555,7 @@
       <c r="I344" s="2"/>
       <c r="J344" s="2"/>
     </row>
-    <row r="345" ht="15.75" customHeight="1">
+    <row r="345" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="2"/>
@@ -4511,7 +4567,7 @@
       <c r="I345" s="2"/>
       <c r="J345" s="2"/>
     </row>
-    <row r="346" ht="15.75" customHeight="1">
+    <row r="346" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="2"/>
@@ -4523,7 +4579,7 @@
       <c r="I346" s="2"/>
       <c r="J346" s="2"/>
     </row>
-    <row r="347" ht="15.75" customHeight="1">
+    <row r="347" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="2"/>
@@ -4535,7 +4591,7 @@
       <c r="I347" s="2"/>
       <c r="J347" s="2"/>
     </row>
-    <row r="348" ht="15.75" customHeight="1">
+    <row r="348" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="2"/>
@@ -4547,7 +4603,7 @@
       <c r="I348" s="2"/>
       <c r="J348" s="2"/>
     </row>
-    <row r="349" ht="15.75" customHeight="1">
+    <row r="349" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="2"/>
@@ -4559,7 +4615,7 @@
       <c r="I349" s="2"/>
       <c r="J349" s="2"/>
     </row>
-    <row r="350" ht="15.75" customHeight="1">
+    <row r="350" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="2"/>
@@ -4571,7 +4627,7 @@
       <c r="I350" s="2"/>
       <c r="J350" s="2"/>
     </row>
-    <row r="351" ht="15.75" customHeight="1">
+    <row r="351" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="2"/>
@@ -4583,7 +4639,7 @@
       <c r="I351" s="2"/>
       <c r="J351" s="2"/>
     </row>
-    <row r="352" ht="15.75" customHeight="1">
+    <row r="352" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="2"/>
@@ -4595,7 +4651,7 @@
       <c r="I352" s="2"/>
       <c r="J352" s="2"/>
     </row>
-    <row r="353" ht="15.75" customHeight="1">
+    <row r="353" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="2"/>
@@ -4607,7 +4663,7 @@
       <c r="I353" s="2"/>
       <c r="J353" s="2"/>
     </row>
-    <row r="354" ht="15.75" customHeight="1">
+    <row r="354" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="2"/>
@@ -4619,7 +4675,7 @@
       <c r="I354" s="2"/>
       <c r="J354" s="2"/>
     </row>
-    <row r="355" ht="15.75" customHeight="1">
+    <row r="355" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="2"/>
@@ -4631,7 +4687,7 @@
       <c r="I355" s="2"/>
       <c r="J355" s="2"/>
     </row>
-    <row r="356" ht="15.75" customHeight="1">
+    <row r="356" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="2"/>
@@ -4643,7 +4699,7 @@
       <c r="I356" s="2"/>
       <c r="J356" s="2"/>
     </row>
-    <row r="357" ht="15.75" customHeight="1">
+    <row r="357" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="2"/>
@@ -4655,7 +4711,7 @@
       <c r="I357" s="2"/>
       <c r="J357" s="2"/>
     </row>
-    <row r="358" ht="15.75" customHeight="1">
+    <row r="358" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="2"/>
@@ -4667,7 +4723,7 @@
       <c r="I358" s="2"/>
       <c r="J358" s="2"/>
     </row>
-    <row r="359" ht="15.75" customHeight="1">
+    <row r="359" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="2"/>
@@ -4679,7 +4735,7 @@
       <c r="I359" s="2"/>
       <c r="J359" s="2"/>
     </row>
-    <row r="360" ht="15.75" customHeight="1">
+    <row r="360" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="2"/>
@@ -4691,7 +4747,7 @@
       <c r="I360" s="2"/>
       <c r="J360" s="2"/>
     </row>
-    <row r="361" ht="15.75" customHeight="1">
+    <row r="361" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="2"/>
@@ -4703,7 +4759,7 @@
       <c r="I361" s="2"/>
       <c r="J361" s="2"/>
     </row>
-    <row r="362" ht="15.75" customHeight="1">
+    <row r="362" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="2"/>
@@ -4715,7 +4771,7 @@
       <c r="I362" s="2"/>
       <c r="J362" s="2"/>
     </row>
-    <row r="363" ht="15.75" customHeight="1">
+    <row r="363" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="2"/>
@@ -4727,7 +4783,7 @@
       <c r="I363" s="2"/>
       <c r="J363" s="2"/>
     </row>
-    <row r="364" ht="15.75" customHeight="1">
+    <row r="364" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="2"/>
@@ -4739,7 +4795,7 @@
       <c r="I364" s="2"/>
       <c r="J364" s="2"/>
     </row>
-    <row r="365" ht="15.75" customHeight="1">
+    <row r="365" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="2"/>
@@ -4751,7 +4807,7 @@
       <c r="I365" s="2"/>
       <c r="J365" s="2"/>
     </row>
-    <row r="366" ht="15.75" customHeight="1">
+    <row r="366" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
@@ -4763,7 +4819,7 @@
       <c r="I366" s="2"/>
       <c r="J366" s="2"/>
     </row>
-    <row r="367" ht="15.75" customHeight="1">
+    <row r="367" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="2"/>
@@ -4775,7 +4831,7 @@
       <c r="I367" s="2"/>
       <c r="J367" s="2"/>
     </row>
-    <row r="368" ht="15.75" customHeight="1">
+    <row r="368" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="2"/>
@@ -4787,7 +4843,7 @@
       <c r="I368" s="2"/>
       <c r="J368" s="2"/>
     </row>
-    <row r="369" ht="15.75" customHeight="1">
+    <row r="369" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="2"/>
@@ -4799,7 +4855,7 @@
       <c r="I369" s="2"/>
       <c r="J369" s="2"/>
     </row>
-    <row r="370" ht="15.75" customHeight="1">
+    <row r="370" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="2"/>
@@ -4811,7 +4867,7 @@
       <c r="I370" s="2"/>
       <c r="J370" s="2"/>
     </row>
-    <row r="371" ht="15.75" customHeight="1">
+    <row r="371" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="2"/>
@@ -4823,7 +4879,7 @@
       <c r="I371" s="2"/>
       <c r="J371" s="2"/>
     </row>
-    <row r="372" ht="15.75" customHeight="1">
+    <row r="372" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="2"/>
@@ -4835,7 +4891,7 @@
       <c r="I372" s="2"/>
       <c r="J372" s="2"/>
     </row>
-    <row r="373" ht="15.75" customHeight="1">
+    <row r="373" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="2"/>
@@ -4847,7 +4903,7 @@
       <c r="I373" s="2"/>
       <c r="J373" s="2"/>
     </row>
-    <row r="374" ht="15.75" customHeight="1">
+    <row r="374" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="2"/>
@@ -4859,7 +4915,7 @@
       <c r="I374" s="2"/>
       <c r="J374" s="2"/>
     </row>
-    <row r="375" ht="15.75" customHeight="1">
+    <row r="375" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="2"/>
@@ -4871,7 +4927,7 @@
       <c r="I375" s="2"/>
       <c r="J375" s="2"/>
     </row>
-    <row r="376" ht="15.75" customHeight="1">
+    <row r="376" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="2"/>
@@ -4883,7 +4939,7 @@
       <c r="I376" s="2"/>
       <c r="J376" s="2"/>
     </row>
-    <row r="377" ht="15.75" customHeight="1">
+    <row r="377" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="2"/>
@@ -4895,7 +4951,7 @@
       <c r="I377" s="2"/>
       <c r="J377" s="2"/>
     </row>
-    <row r="378" ht="15.75" customHeight="1">
+    <row r="378" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="2"/>
@@ -4907,7 +4963,7 @@
       <c r="I378" s="2"/>
       <c r="J378" s="2"/>
     </row>
-    <row r="379" ht="15.75" customHeight="1">
+    <row r="379" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="2"/>
@@ -4919,7 +4975,7 @@
       <c r="I379" s="2"/>
       <c r="J379" s="2"/>
     </row>
-    <row r="380" ht="15.75" customHeight="1">
+    <row r="380" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="2"/>
@@ -4931,7 +4987,7 @@
       <c r="I380" s="2"/>
       <c r="J380" s="2"/>
     </row>
-    <row r="381" ht="15.75" customHeight="1">
+    <row r="381" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="2"/>
@@ -4943,7 +4999,7 @@
       <c r="I381" s="2"/>
       <c r="J381" s="2"/>
     </row>
-    <row r="382" ht="15.75" customHeight="1">
+    <row r="382" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="2"/>
@@ -4955,7 +5011,7 @@
       <c r="I382" s="2"/>
       <c r="J382" s="2"/>
     </row>
-    <row r="383" ht="15.75" customHeight="1">
+    <row r="383" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="2"/>
@@ -4967,7 +5023,7 @@
       <c r="I383" s="2"/>
       <c r="J383" s="2"/>
     </row>
-    <row r="384" ht="15.75" customHeight="1">
+    <row r="384" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="2"/>
@@ -4979,7 +5035,7 @@
       <c r="I384" s="2"/>
       <c r="J384" s="2"/>
     </row>
-    <row r="385" ht="15.75" customHeight="1">
+    <row r="385" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="2"/>
@@ -4991,7 +5047,7 @@
       <c r="I385" s="2"/>
       <c r="J385" s="2"/>
     </row>
-    <row r="386" ht="15.75" customHeight="1">
+    <row r="386" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="2"/>
@@ -5003,7 +5059,7 @@
       <c r="I386" s="2"/>
       <c r="J386" s="2"/>
     </row>
-    <row r="387" ht="15.75" customHeight="1">
+    <row r="387" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="2"/>
@@ -5015,7 +5071,7 @@
       <c r="I387" s="2"/>
       <c r="J387" s="2"/>
     </row>
-    <row r="388" ht="15.75" customHeight="1">
+    <row r="388" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="2"/>
@@ -5027,7 +5083,7 @@
       <c r="I388" s="2"/>
       <c r="J388" s="2"/>
     </row>
-    <row r="389" ht="15.75" customHeight="1">
+    <row r="389" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="2"/>
@@ -5039,7 +5095,7 @@
       <c r="I389" s="2"/>
       <c r="J389" s="2"/>
     </row>
-    <row r="390" ht="15.75" customHeight="1">
+    <row r="390" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="2"/>
@@ -5051,7 +5107,7 @@
       <c r="I390" s="2"/>
       <c r="J390" s="2"/>
     </row>
-    <row r="391" ht="15.75" customHeight="1">
+    <row r="391" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="2"/>
@@ -5063,7 +5119,7 @@
       <c r="I391" s="2"/>
       <c r="J391" s="2"/>
     </row>
-    <row r="392" ht="15.75" customHeight="1">
+    <row r="392" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="2"/>
@@ -5075,7 +5131,7 @@
       <c r="I392" s="2"/>
       <c r="J392" s="2"/>
     </row>
-    <row r="393" ht="15.75" customHeight="1">
+    <row r="393" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="2"/>
@@ -5087,7 +5143,7 @@
       <c r="I393" s="2"/>
       <c r="J393" s="2"/>
     </row>
-    <row r="394" ht="15.75" customHeight="1">
+    <row r="394" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="2"/>
@@ -5099,7 +5155,7 @@
       <c r="I394" s="2"/>
       <c r="J394" s="2"/>
     </row>
-    <row r="395" ht="15.75" customHeight="1">
+    <row r="395" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="2"/>
@@ -5111,7 +5167,7 @@
       <c r="I395" s="2"/>
       <c r="J395" s="2"/>
     </row>
-    <row r="396" ht="15.75" customHeight="1">
+    <row r="396" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="2"/>
@@ -5123,7 +5179,7 @@
       <c r="I396" s="2"/>
       <c r="J396" s="2"/>
     </row>
-    <row r="397" ht="15.75" customHeight="1">
+    <row r="397" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="2"/>
@@ -5135,7 +5191,7 @@
       <c r="I397" s="2"/>
       <c r="J397" s="2"/>
     </row>
-    <row r="398" ht="15.75" customHeight="1">
+    <row r="398" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="2"/>
@@ -5147,7 +5203,7 @@
       <c r="I398" s="2"/>
       <c r="J398" s="2"/>
     </row>
-    <row r="399" ht="15.75" customHeight="1">
+    <row r="399" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="2"/>
@@ -5159,7 +5215,7 @@
       <c r="I399" s="2"/>
       <c r="J399" s="2"/>
     </row>
-    <row r="400" ht="15.75" customHeight="1">
+    <row r="400" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="2"/>
@@ -5171,7 +5227,7 @@
       <c r="I400" s="2"/>
       <c r="J400" s="2"/>
     </row>
-    <row r="401" ht="15.75" customHeight="1">
+    <row r="401" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="2"/>
@@ -5183,7 +5239,7 @@
       <c r="I401" s="2"/>
       <c r="J401" s="2"/>
     </row>
-    <row r="402" ht="15.75" customHeight="1">
+    <row r="402" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="2"/>
@@ -5195,7 +5251,7 @@
       <c r="I402" s="2"/>
       <c r="J402" s="2"/>
     </row>
-    <row r="403" ht="15.75" customHeight="1">
+    <row r="403" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="2"/>
@@ -5207,7 +5263,7 @@
       <c r="I403" s="2"/>
       <c r="J403" s="2"/>
     </row>
-    <row r="404" ht="15.75" customHeight="1">
+    <row r="404" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="2"/>
@@ -5219,7 +5275,7 @@
       <c r="I404" s="2"/>
       <c r="J404" s="2"/>
     </row>
-    <row r="405" ht="15.75" customHeight="1">
+    <row r="405" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="2"/>
@@ -5231,7 +5287,7 @@
       <c r="I405" s="2"/>
       <c r="J405" s="2"/>
     </row>
-    <row r="406" ht="15.75" customHeight="1">
+    <row r="406" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="2"/>
@@ -5243,7 +5299,7 @@
       <c r="I406" s="2"/>
       <c r="J406" s="2"/>
     </row>
-    <row r="407" ht="15.75" customHeight="1">
+    <row r="407" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="2"/>
@@ -5255,7 +5311,7 @@
       <c r="I407" s="2"/>
       <c r="J407" s="2"/>
     </row>
-    <row r="408" ht="15.75" customHeight="1">
+    <row r="408" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="2"/>
@@ -5267,7 +5323,7 @@
       <c r="I408" s="2"/>
       <c r="J408" s="2"/>
     </row>
-    <row r="409" ht="15.75" customHeight="1">
+    <row r="409" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="2"/>
@@ -5279,7 +5335,7 @@
       <c r="I409" s="2"/>
       <c r="J409" s="2"/>
     </row>
-    <row r="410" ht="15.75" customHeight="1">
+    <row r="410" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="2"/>
@@ -5291,7 +5347,7 @@
       <c r="I410" s="2"/>
       <c r="J410" s="2"/>
     </row>
-    <row r="411" ht="15.75" customHeight="1">
+    <row r="411" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="2"/>
@@ -5303,7 +5359,7 @@
       <c r="I411" s="2"/>
       <c r="J411" s="2"/>
     </row>
-    <row r="412" ht="15.75" customHeight="1">
+    <row r="412" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="2"/>
@@ -5315,7 +5371,7 @@
       <c r="I412" s="2"/>
       <c r="J412" s="2"/>
     </row>
-    <row r="413" ht="15.75" customHeight="1">
+    <row r="413" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="2"/>
@@ -5327,7 +5383,7 @@
       <c r="I413" s="2"/>
       <c r="J413" s="2"/>
     </row>
-    <row r="414" ht="15.75" customHeight="1">
+    <row r="414" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="2"/>
@@ -5339,7 +5395,7 @@
       <c r="I414" s="2"/>
       <c r="J414" s="2"/>
     </row>
-    <row r="415" ht="15.75" customHeight="1">
+    <row r="415" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="2"/>
@@ -5351,7 +5407,7 @@
       <c r="I415" s="2"/>
       <c r="J415" s="2"/>
     </row>
-    <row r="416" ht="15.75" customHeight="1">
+    <row r="416" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="2"/>
@@ -5363,7 +5419,7 @@
       <c r="I416" s="2"/>
       <c r="J416" s="2"/>
     </row>
-    <row r="417" ht="15.75" customHeight="1">
+    <row r="417" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="2"/>
@@ -5375,7 +5431,7 @@
       <c r="I417" s="2"/>
       <c r="J417" s="2"/>
     </row>
-    <row r="418" ht="15.75" customHeight="1">
+    <row r="418" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="2"/>
@@ -5387,7 +5443,7 @@
       <c r="I418" s="2"/>
       <c r="J418" s="2"/>
     </row>
-    <row r="419" ht="15.75" customHeight="1">
+    <row r="419" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="2"/>
@@ -5399,7 +5455,7 @@
       <c r="I419" s="2"/>
       <c r="J419" s="2"/>
     </row>
-    <row r="420" ht="15.75" customHeight="1">
+    <row r="420" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="2"/>
@@ -5411,7 +5467,7 @@
       <c r="I420" s="2"/>
       <c r="J420" s="2"/>
     </row>
-    <row r="421" ht="15.75" customHeight="1">
+    <row r="421" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="2"/>
@@ -5423,7 +5479,7 @@
       <c r="I421" s="2"/>
       <c r="J421" s="2"/>
     </row>
-    <row r="422" ht="15.75" customHeight="1">
+    <row r="422" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="2"/>
@@ -5435,7 +5491,7 @@
       <c r="I422" s="2"/>
       <c r="J422" s="2"/>
     </row>
-    <row r="423" ht="15.75" customHeight="1">
+    <row r="423" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="2"/>
@@ -5447,7 +5503,7 @@
       <c r="I423" s="2"/>
       <c r="J423" s="2"/>
     </row>
-    <row r="424" ht="15.75" customHeight="1">
+    <row r="424" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="2"/>
@@ -5459,7 +5515,7 @@
       <c r="I424" s="2"/>
       <c r="J424" s="2"/>
     </row>
-    <row r="425" ht="15.75" customHeight="1">
+    <row r="425" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="2"/>
@@ -5471,7 +5527,7 @@
       <c r="I425" s="2"/>
       <c r="J425" s="2"/>
     </row>
-    <row r="426" ht="15.75" customHeight="1">
+    <row r="426" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="2"/>
@@ -5483,7 +5539,7 @@
       <c r="I426" s="2"/>
       <c r="J426" s="2"/>
     </row>
-    <row r="427" ht="15.75" customHeight="1">
+    <row r="427" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="2"/>
@@ -5495,7 +5551,7 @@
       <c r="I427" s="2"/>
       <c r="J427" s="2"/>
     </row>
-    <row r="428" ht="15.75" customHeight="1">
+    <row r="428" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="2"/>
@@ -5507,7 +5563,7 @@
       <c r="I428" s="2"/>
       <c r="J428" s="2"/>
     </row>
-    <row r="429" ht="15.75" customHeight="1">
+    <row r="429" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="2"/>
@@ -5519,7 +5575,7 @@
       <c r="I429" s="2"/>
       <c r="J429" s="2"/>
     </row>
-    <row r="430" ht="15.75" customHeight="1">
+    <row r="430" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="2"/>
@@ -5531,7 +5587,7 @@
       <c r="I430" s="2"/>
       <c r="J430" s="2"/>
     </row>
-    <row r="431" ht="15.75" customHeight="1">
+    <row r="431" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="2"/>
@@ -5543,7 +5599,7 @@
       <c r="I431" s="2"/>
       <c r="J431" s="2"/>
     </row>
-    <row r="432" ht="15.75" customHeight="1">
+    <row r="432" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="2"/>
@@ -5555,7 +5611,7 @@
       <c r="I432" s="2"/>
       <c r="J432" s="2"/>
     </row>
-    <row r="433" ht="15.75" customHeight="1">
+    <row r="433" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="2"/>
@@ -5567,7 +5623,7 @@
       <c r="I433" s="2"/>
       <c r="J433" s="2"/>
     </row>
-    <row r="434" ht="15.75" customHeight="1">
+    <row r="434" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="2"/>
@@ -5579,7 +5635,7 @@
       <c r="I434" s="2"/>
       <c r="J434" s="2"/>
     </row>
-    <row r="435" ht="15.75" customHeight="1">
+    <row r="435" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
@@ -5591,7 +5647,7 @@
       <c r="I435" s="2"/>
       <c r="J435" s="2"/>
     </row>
-    <row r="436" ht="15.75" customHeight="1">
+    <row r="436" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="2"/>
@@ -5603,7 +5659,7 @@
       <c r="I436" s="2"/>
       <c r="J436" s="2"/>
     </row>
-    <row r="437" ht="15.75" customHeight="1">
+    <row r="437" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="2"/>
@@ -5615,7 +5671,7 @@
       <c r="I437" s="2"/>
       <c r="J437" s="2"/>
     </row>
-    <row r="438" ht="15.75" customHeight="1">
+    <row r="438" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="2"/>
@@ -5627,7 +5683,7 @@
       <c r="I438" s="2"/>
       <c r="J438" s="2"/>
     </row>
-    <row r="439" ht="15.75" customHeight="1">
+    <row r="439" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="2"/>
@@ -5639,7 +5695,7 @@
       <c r="I439" s="2"/>
       <c r="J439" s="2"/>
     </row>
-    <row r="440" ht="15.75" customHeight="1">
+    <row r="440" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="2"/>
@@ -5651,7 +5707,7 @@
       <c r="I440" s="2"/>
       <c r="J440" s="2"/>
     </row>
-    <row r="441" ht="15.75" customHeight="1">
+    <row r="441" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="2"/>
@@ -5663,7 +5719,7 @@
       <c r="I441" s="2"/>
       <c r="J441" s="2"/>
     </row>
-    <row r="442" ht="15.75" customHeight="1">
+    <row r="442" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="2"/>
@@ -5675,7 +5731,7 @@
       <c r="I442" s="2"/>
       <c r="J442" s="2"/>
     </row>
-    <row r="443" ht="15.75" customHeight="1">
+    <row r="443" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="2"/>
@@ -5687,7 +5743,7 @@
       <c r="I443" s="2"/>
       <c r="J443" s="2"/>
     </row>
-    <row r="444" ht="15.75" customHeight="1">
+    <row r="444" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="2"/>
@@ -5699,7 +5755,7 @@
       <c r="I444" s="2"/>
       <c r="J444" s="2"/>
     </row>
-    <row r="445" ht="15.75" customHeight="1">
+    <row r="445" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="2"/>
@@ -5711,7 +5767,7 @@
       <c r="I445" s="2"/>
       <c r="J445" s="2"/>
     </row>
-    <row r="446" ht="15.75" customHeight="1">
+    <row r="446" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="2"/>
@@ -5723,7 +5779,7 @@
       <c r="I446" s="2"/>
       <c r="J446" s="2"/>
     </row>
-    <row r="447" ht="15.75" customHeight="1">
+    <row r="447" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="2"/>
@@ -5735,7 +5791,7 @@
       <c r="I447" s="2"/>
       <c r="J447" s="2"/>
     </row>
-    <row r="448" ht="15.75" customHeight="1">
+    <row r="448" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="2"/>
@@ -5747,7 +5803,7 @@
       <c r="I448" s="2"/>
       <c r="J448" s="2"/>
     </row>
-    <row r="449" ht="15.75" customHeight="1">
+    <row r="449" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="2"/>
@@ -5759,7 +5815,7 @@
       <c r="I449" s="2"/>
       <c r="J449" s="2"/>
     </row>
-    <row r="450" ht="15.75" customHeight="1">
+    <row r="450" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="2"/>
@@ -5771,7 +5827,7 @@
       <c r="I450" s="2"/>
       <c r="J450" s="2"/>
     </row>
-    <row r="451" ht="15.75" customHeight="1">
+    <row r="451" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="2"/>
@@ -5783,7 +5839,7 @@
       <c r="I451" s="2"/>
       <c r="J451" s="2"/>
     </row>
-    <row r="452" ht="15.75" customHeight="1">
+    <row r="452" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="2"/>
@@ -5795,7 +5851,7 @@
       <c r="I452" s="2"/>
       <c r="J452" s="2"/>
     </row>
-    <row r="453" ht="15.75" customHeight="1">
+    <row r="453" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="2"/>
@@ -5807,7 +5863,7 @@
       <c r="I453" s="2"/>
       <c r="J453" s="2"/>
     </row>
-    <row r="454" ht="15.75" customHeight="1">
+    <row r="454" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="2"/>
@@ -5819,7 +5875,7 @@
       <c r="I454" s="2"/>
       <c r="J454" s="2"/>
     </row>
-    <row r="455" ht="15.75" customHeight="1">
+    <row r="455" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="2"/>
@@ -5831,7 +5887,7 @@
       <c r="I455" s="2"/>
       <c r="J455" s="2"/>
     </row>
-    <row r="456" ht="15.75" customHeight="1">
+    <row r="456" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="2"/>
@@ -5843,7 +5899,7 @@
       <c r="I456" s="2"/>
       <c r="J456" s="2"/>
     </row>
-    <row r="457" ht="15.75" customHeight="1">
+    <row r="457" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="2"/>
@@ -5855,7 +5911,7 @@
       <c r="I457" s="2"/>
       <c r="J457" s="2"/>
     </row>
-    <row r="458" ht="15.75" customHeight="1">
+    <row r="458" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="2"/>
@@ -5867,7 +5923,7 @@
       <c r="I458" s="2"/>
       <c r="J458" s="2"/>
     </row>
-    <row r="459" ht="15.75" customHeight="1">
+    <row r="459" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="2"/>
@@ -5879,7 +5935,7 @@
       <c r="I459" s="2"/>
       <c r="J459" s="2"/>
     </row>
-    <row r="460" ht="15.75" customHeight="1">
+    <row r="460" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="2"/>
@@ -5891,7 +5947,7 @@
       <c r="I460" s="2"/>
       <c r="J460" s="2"/>
     </row>
-    <row r="461" ht="15.75" customHeight="1">
+    <row r="461" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="2"/>
@@ -5903,7 +5959,7 @@
       <c r="I461" s="2"/>
       <c r="J461" s="2"/>
     </row>
-    <row r="462" ht="15.75" customHeight="1">
+    <row r="462" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="2"/>
@@ -5915,7 +5971,7 @@
       <c r="I462" s="2"/>
       <c r="J462" s="2"/>
     </row>
-    <row r="463" ht="15.75" customHeight="1">
+    <row r="463" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="2"/>
@@ -5927,7 +5983,7 @@
       <c r="I463" s="2"/>
       <c r="J463" s="2"/>
     </row>
-    <row r="464" ht="15.75" customHeight="1">
+    <row r="464" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="2"/>
@@ -5939,7 +5995,7 @@
       <c r="I464" s="2"/>
       <c r="J464" s="2"/>
     </row>
-    <row r="465" ht="15.75" customHeight="1">
+    <row r="465" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="2"/>
@@ -5951,7 +6007,7 @@
       <c r="I465" s="2"/>
       <c r="J465" s="2"/>
     </row>
-    <row r="466" ht="15.75" customHeight="1">
+    <row r="466" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="2"/>
@@ -5963,7 +6019,7 @@
       <c r="I466" s="2"/>
       <c r="J466" s="2"/>
     </row>
-    <row r="467" ht="15.75" customHeight="1">
+    <row r="467" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="2"/>
@@ -5975,7 +6031,7 @@
       <c r="I467" s="2"/>
       <c r="J467" s="2"/>
     </row>
-    <row r="468" ht="15.75" customHeight="1">
+    <row r="468" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="2"/>
@@ -5987,7 +6043,7 @@
       <c r="I468" s="2"/>
       <c r="J468" s="2"/>
     </row>
-    <row r="469" ht="15.75" customHeight="1">
+    <row r="469" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="2"/>
@@ -5999,7 +6055,7 @@
       <c r="I469" s="2"/>
       <c r="J469" s="2"/>
     </row>
-    <row r="470" ht="15.75" customHeight="1">
+    <row r="470" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="2"/>
@@ -6011,7 +6067,7 @@
       <c r="I470" s="2"/>
       <c r="J470" s="2"/>
     </row>
-    <row r="471" ht="15.75" customHeight="1">
+    <row r="471" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="2"/>
@@ -6023,7 +6079,7 @@
       <c r="I471" s="2"/>
       <c r="J471" s="2"/>
     </row>
-    <row r="472" ht="15.75" customHeight="1">
+    <row r="472" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="2"/>
@@ -6035,7 +6091,7 @@
       <c r="I472" s="2"/>
       <c r="J472" s="2"/>
     </row>
-    <row r="473" ht="15.75" customHeight="1">
+    <row r="473" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="2"/>
@@ -6047,7 +6103,7 @@
       <c r="I473" s="2"/>
       <c r="J473" s="2"/>
     </row>
-    <row r="474" ht="15.75" customHeight="1">
+    <row r="474" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="2"/>
@@ -6059,7 +6115,7 @@
       <c r="I474" s="2"/>
       <c r="J474" s="2"/>
     </row>
-    <row r="475" ht="15.75" customHeight="1">
+    <row r="475" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="2"/>
@@ -6071,7 +6127,7 @@
       <c r="I475" s="2"/>
       <c r="J475" s="2"/>
     </row>
-    <row r="476" ht="15.75" customHeight="1">
+    <row r="476" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="2"/>
@@ -6083,7 +6139,7 @@
       <c r="I476" s="2"/>
       <c r="J476" s="2"/>
     </row>
-    <row r="477" ht="15.75" customHeight="1">
+    <row r="477" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="2"/>
@@ -6095,7 +6151,7 @@
       <c r="I477" s="2"/>
       <c r="J477" s="2"/>
     </row>
-    <row r="478" ht="15.75" customHeight="1">
+    <row r="478" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="2"/>
@@ -6107,7 +6163,7 @@
       <c r="I478" s="2"/>
       <c r="J478" s="2"/>
     </row>
-    <row r="479" ht="15.75" customHeight="1">
+    <row r="479" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="2"/>
@@ -6119,7 +6175,7 @@
       <c r="I479" s="2"/>
       <c r="J479" s="2"/>
     </row>
-    <row r="480" ht="15.75" customHeight="1">
+    <row r="480" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="2"/>
@@ -6131,7 +6187,7 @@
       <c r="I480" s="2"/>
       <c r="J480" s="2"/>
     </row>
-    <row r="481" ht="15.75" customHeight="1">
+    <row r="481" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="2"/>
@@ -6143,7 +6199,7 @@
       <c r="I481" s="2"/>
       <c r="J481" s="2"/>
     </row>
-    <row r="482" ht="15.75" customHeight="1">
+    <row r="482" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="2"/>
@@ -6155,7 +6211,7 @@
       <c r="I482" s="2"/>
       <c r="J482" s="2"/>
     </row>
-    <row r="483" ht="15.75" customHeight="1">
+    <row r="483" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="2"/>
@@ -6167,7 +6223,7 @@
       <c r="I483" s="2"/>
       <c r="J483" s="2"/>
     </row>
-    <row r="484" ht="15.75" customHeight="1">
+    <row r="484" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="2"/>
@@ -6179,7 +6235,7 @@
       <c r="I484" s="2"/>
       <c r="J484" s="2"/>
     </row>
-    <row r="485" ht="15.75" customHeight="1">
+    <row r="485" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="2"/>
@@ -6191,7 +6247,7 @@
       <c r="I485" s="2"/>
       <c r="J485" s="2"/>
     </row>
-    <row r="486" ht="15.75" customHeight="1">
+    <row r="486" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="2"/>
@@ -6203,7 +6259,7 @@
       <c r="I486" s="2"/>
       <c r="J486" s="2"/>
     </row>
-    <row r="487" ht="15.75" customHeight="1">
+    <row r="487" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="2"/>
@@ -6215,7 +6271,7 @@
       <c r="I487" s="2"/>
       <c r="J487" s="2"/>
     </row>
-    <row r="488" ht="15.75" customHeight="1">
+    <row r="488" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="2"/>
@@ -6227,7 +6283,7 @@
       <c r="I488" s="2"/>
       <c r="J488" s="2"/>
     </row>
-    <row r="489" ht="15.75" customHeight="1">
+    <row r="489" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="2"/>
@@ -6239,7 +6295,7 @@
       <c r="I489" s="2"/>
       <c r="J489" s="2"/>
     </row>
-    <row r="490" ht="15.75" customHeight="1">
+    <row r="490" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="2"/>
@@ -6251,7 +6307,7 @@
       <c r="I490" s="2"/>
       <c r="J490" s="2"/>
     </row>
-    <row r="491" ht="15.75" customHeight="1">
+    <row r="491" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="2"/>
@@ -6263,7 +6319,7 @@
       <c r="I491" s="2"/>
       <c r="J491" s="2"/>
     </row>
-    <row r="492" ht="15.75" customHeight="1">
+    <row r="492" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="2"/>
@@ -6275,7 +6331,7 @@
       <c r="I492" s="2"/>
       <c r="J492" s="2"/>
     </row>
-    <row r="493" ht="15.75" customHeight="1">
+    <row r="493" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="2"/>
@@ -6287,7 +6343,7 @@
       <c r="I493" s="2"/>
       <c r="J493" s="2"/>
     </row>
-    <row r="494" ht="15.75" customHeight="1">
+    <row r="494" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="2"/>
@@ -6299,7 +6355,7 @@
       <c r="I494" s="2"/>
       <c r="J494" s="2"/>
     </row>
-    <row r="495" ht="15.75" customHeight="1">
+    <row r="495" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="2"/>
@@ -6311,7 +6367,7 @@
       <c r="I495" s="2"/>
       <c r="J495" s="2"/>
     </row>
-    <row r="496" ht="15.75" customHeight="1">
+    <row r="496" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="2"/>
@@ -6323,7 +6379,7 @@
       <c r="I496" s="2"/>
       <c r="J496" s="2"/>
     </row>
-    <row r="497" ht="15.75" customHeight="1">
+    <row r="497" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="2"/>
@@ -6335,7 +6391,7 @@
       <c r="I497" s="2"/>
       <c r="J497" s="2"/>
     </row>
-    <row r="498" ht="15.75" customHeight="1">
+    <row r="498" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="2"/>
@@ -6347,7 +6403,7 @@
       <c r="I498" s="2"/>
       <c r="J498" s="2"/>
     </row>
-    <row r="499" ht="15.75" customHeight="1">
+    <row r="499" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="2"/>
@@ -6359,7 +6415,7 @@
       <c r="I499" s="2"/>
       <c r="J499" s="2"/>
     </row>
-    <row r="500" ht="15.75" customHeight="1">
+    <row r="500" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="2"/>
@@ -6371,7 +6427,7 @@
       <c r="I500" s="2"/>
       <c r="J500" s="2"/>
     </row>
-    <row r="501" ht="15.75" customHeight="1">
+    <row r="501" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
       <c r="C501" s="2"/>
@@ -6383,7 +6439,7 @@
       <c r="I501" s="2"/>
       <c r="J501" s="2"/>
     </row>
-    <row r="502" ht="15.75" customHeight="1">
+    <row r="502" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
       <c r="C502" s="2"/>
@@ -6395,7 +6451,7 @@
       <c r="I502" s="2"/>
       <c r="J502" s="2"/>
     </row>
-    <row r="503" ht="15.75" customHeight="1">
+    <row r="503" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
       <c r="C503" s="2"/>
@@ -6407,7 +6463,7 @@
       <c r="I503" s="2"/>
       <c r="J503" s="2"/>
     </row>
-    <row r="504" ht="15.75" customHeight="1">
+    <row r="504" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
       <c r="C504" s="2"/>
@@ -6419,7 +6475,7 @@
       <c r="I504" s="2"/>
       <c r="J504" s="2"/>
     </row>
-    <row r="505" ht="15.75" customHeight="1">
+    <row r="505" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
       <c r="C505" s="2"/>
@@ -6431,7 +6487,7 @@
       <c r="I505" s="2"/>
       <c r="J505" s="2"/>
     </row>
-    <row r="506" ht="15.75" customHeight="1">
+    <row r="506" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
       <c r="C506" s="2"/>
@@ -6443,7 +6499,7 @@
       <c r="I506" s="2"/>
       <c r="J506" s="2"/>
     </row>
-    <row r="507" ht="15.75" customHeight="1">
+    <row r="507" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
       <c r="C507" s="2"/>
@@ -6455,7 +6511,7 @@
       <c r="I507" s="2"/>
       <c r="J507" s="2"/>
     </row>
-    <row r="508" ht="15.75" customHeight="1">
+    <row r="508" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
       <c r="C508" s="2"/>
@@ -6467,7 +6523,7 @@
       <c r="I508" s="2"/>
       <c r="J508" s="2"/>
     </row>
-    <row r="509" ht="15.75" customHeight="1">
+    <row r="509" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
       <c r="C509" s="2"/>
@@ -6479,7 +6535,7 @@
       <c r="I509" s="2"/>
       <c r="J509" s="2"/>
     </row>
-    <row r="510" ht="15.75" customHeight="1">
+    <row r="510" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
       <c r="C510" s="2"/>
@@ -6491,7 +6547,7 @@
       <c r="I510" s="2"/>
       <c r="J510" s="2"/>
     </row>
-    <row r="511" ht="15.75" customHeight="1">
+    <row r="511" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
       <c r="C511" s="2"/>
@@ -6503,7 +6559,7 @@
       <c r="I511" s="2"/>
       <c r="J511" s="2"/>
     </row>
-    <row r="512" ht="15.75" customHeight="1">
+    <row r="512" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
       <c r="C512" s="2"/>
@@ -6515,7 +6571,7 @@
       <c r="I512" s="2"/>
       <c r="J512" s="2"/>
     </row>
-    <row r="513" ht="15.75" customHeight="1">
+    <row r="513" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
       <c r="C513" s="2"/>
@@ -6527,7 +6583,7 @@
       <c r="I513" s="2"/>
       <c r="J513" s="2"/>
     </row>
-    <row r="514" ht="15.75" customHeight="1">
+    <row r="514" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
       <c r="C514" s="2"/>
@@ -6539,7 +6595,7 @@
       <c r="I514" s="2"/>
       <c r="J514" s="2"/>
     </row>
-    <row r="515" ht="15.75" customHeight="1">
+    <row r="515" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
       <c r="C515" s="2"/>
@@ -6551,7 +6607,7 @@
       <c r="I515" s="2"/>
       <c r="J515" s="2"/>
     </row>
-    <row r="516" ht="15.75" customHeight="1">
+    <row r="516" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
       <c r="C516" s="2"/>
@@ -6563,7 +6619,7 @@
       <c r="I516" s="2"/>
       <c r="J516" s="2"/>
     </row>
-    <row r="517" ht="15.75" customHeight="1">
+    <row r="517" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
       <c r="C517" s="2"/>
@@ -6575,7 +6631,7 @@
       <c r="I517" s="2"/>
       <c r="J517" s="2"/>
     </row>
-    <row r="518" ht="15.75" customHeight="1">
+    <row r="518" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
       <c r="C518" s="2"/>
@@ -6587,7 +6643,7 @@
       <c r="I518" s="2"/>
       <c r="J518" s="2"/>
     </row>
-    <row r="519" ht="15.75" customHeight="1">
+    <row r="519" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
       <c r="C519" s="2"/>
@@ -6599,7 +6655,7 @@
       <c r="I519" s="2"/>
       <c r="J519" s="2"/>
     </row>
-    <row r="520" ht="15.75" customHeight="1">
+    <row r="520" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
       <c r="C520" s="2"/>
@@ -6611,7 +6667,7 @@
       <c r="I520" s="2"/>
       <c r="J520" s="2"/>
     </row>
-    <row r="521" ht="15.75" customHeight="1">
+    <row r="521" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
       <c r="C521" s="2"/>
@@ -6623,7 +6679,7 @@
       <c r="I521" s="2"/>
       <c r="J521" s="2"/>
     </row>
-    <row r="522" ht="15.75" customHeight="1">
+    <row r="522" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
       <c r="C522" s="2"/>
@@ -6635,7 +6691,7 @@
       <c r="I522" s="2"/>
       <c r="J522" s="2"/>
     </row>
-    <row r="523" ht="15.75" customHeight="1">
+    <row r="523" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
       <c r="C523" s="2"/>
@@ -6647,7 +6703,7 @@
       <c r="I523" s="2"/>
       <c r="J523" s="2"/>
     </row>
-    <row r="524" ht="15.75" customHeight="1">
+    <row r="524" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
       <c r="C524" s="2"/>
@@ -6659,7 +6715,7 @@
       <c r="I524" s="2"/>
       <c r="J524" s="2"/>
     </row>
-    <row r="525" ht="15.75" customHeight="1">
+    <row r="525" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
       <c r="C525" s="2"/>
@@ -6671,7 +6727,7 @@
       <c r="I525" s="2"/>
       <c r="J525" s="2"/>
     </row>
-    <row r="526" ht="15.75" customHeight="1">
+    <row r="526" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
       <c r="C526" s="2"/>
@@ -6683,7 +6739,7 @@
       <c r="I526" s="2"/>
       <c r="J526" s="2"/>
     </row>
-    <row r="527" ht="15.75" customHeight="1">
+    <row r="527" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
       <c r="C527" s="2"/>
@@ -6695,7 +6751,7 @@
       <c r="I527" s="2"/>
       <c r="J527" s="2"/>
     </row>
-    <row r="528" ht="15.75" customHeight="1">
+    <row r="528" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
       <c r="C528" s="2"/>
@@ -6707,7 +6763,7 @@
       <c r="I528" s="2"/>
       <c r="J528" s="2"/>
     </row>
-    <row r="529" ht="15.75" customHeight="1">
+    <row r="529" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
       <c r="C529" s="2"/>
@@ -6719,7 +6775,7 @@
       <c r="I529" s="2"/>
       <c r="J529" s="2"/>
     </row>
-    <row r="530" ht="15.75" customHeight="1">
+    <row r="530" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
       <c r="C530" s="2"/>
@@ -6731,7 +6787,7 @@
       <c r="I530" s="2"/>
       <c r="J530" s="2"/>
     </row>
-    <row r="531" ht="15.75" customHeight="1">
+    <row r="531" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
       <c r="C531" s="2"/>
@@ -6743,7 +6799,7 @@
       <c r="I531" s="2"/>
       <c r="J531" s="2"/>
     </row>
-    <row r="532" ht="15.75" customHeight="1">
+    <row r="532" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
       <c r="C532" s="2"/>
@@ -6755,7 +6811,7 @@
       <c r="I532" s="2"/>
       <c r="J532" s="2"/>
     </row>
-    <row r="533" ht="15.75" customHeight="1">
+    <row r="533" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
       <c r="C533" s="2"/>
@@ -6767,7 +6823,7 @@
       <c r="I533" s="2"/>
       <c r="J533" s="2"/>
     </row>
-    <row r="534" ht="15.75" customHeight="1">
+    <row r="534" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
       <c r="C534" s="2"/>
@@ -6779,7 +6835,7 @@
       <c r="I534" s="2"/>
       <c r="J534" s="2"/>
     </row>
-    <row r="535" ht="15.75" customHeight="1">
+    <row r="535" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
       <c r="C535" s="2"/>
@@ -6791,7 +6847,7 @@
       <c r="I535" s="2"/>
       <c r="J535" s="2"/>
     </row>
-    <row r="536" ht="15.75" customHeight="1">
+    <row r="536" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
       <c r="C536" s="2"/>
@@ -6803,7 +6859,7 @@
       <c r="I536" s="2"/>
       <c r="J536" s="2"/>
     </row>
-    <row r="537" ht="15.75" customHeight="1">
+    <row r="537" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
       <c r="C537" s="2"/>
@@ -6815,7 +6871,7 @@
       <c r="I537" s="2"/>
       <c r="J537" s="2"/>
     </row>
-    <row r="538" ht="15.75" customHeight="1">
+    <row r="538" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
       <c r="C538" s="2"/>
@@ -6827,7 +6883,7 @@
       <c r="I538" s="2"/>
       <c r="J538" s="2"/>
     </row>
-    <row r="539" ht="15.75" customHeight="1">
+    <row r="539" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
       <c r="C539" s="2"/>
@@ -6839,7 +6895,7 @@
       <c r="I539" s="2"/>
       <c r="J539" s="2"/>
     </row>
-    <row r="540" ht="15.75" customHeight="1">
+    <row r="540" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
       <c r="C540" s="2"/>
@@ -6851,7 +6907,7 @@
       <c r="I540" s="2"/>
       <c r="J540" s="2"/>
     </row>
-    <row r="541" ht="15.75" customHeight="1">
+    <row r="541" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
       <c r="C541" s="2"/>
@@ -6863,7 +6919,7 @@
       <c r="I541" s="2"/>
       <c r="J541" s="2"/>
     </row>
-    <row r="542" ht="15.75" customHeight="1">
+    <row r="542" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
       <c r="C542" s="2"/>
@@ -6875,7 +6931,7 @@
       <c r="I542" s="2"/>
       <c r="J542" s="2"/>
     </row>
-    <row r="543" ht="15.75" customHeight="1">
+    <row r="543" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
       <c r="C543" s="2"/>
@@ -6887,7 +6943,7 @@
       <c r="I543" s="2"/>
       <c r="J543" s="2"/>
     </row>
-    <row r="544" ht="15.75" customHeight="1">
+    <row r="544" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
       <c r="C544" s="2"/>
@@ -6899,7 +6955,7 @@
       <c r="I544" s="2"/>
       <c r="J544" s="2"/>
     </row>
-    <row r="545" ht="15.75" customHeight="1">
+    <row r="545" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
       <c r="C545" s="2"/>
@@ -6911,7 +6967,7 @@
       <c r="I545" s="2"/>
       <c r="J545" s="2"/>
     </row>
-    <row r="546" ht="15.75" customHeight="1">
+    <row r="546" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
       <c r="C546" s="2"/>
@@ -6923,7 +6979,7 @@
       <c r="I546" s="2"/>
       <c r="J546" s="2"/>
     </row>
-    <row r="547" ht="15.75" customHeight="1">
+    <row r="547" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
       <c r="C547" s="2"/>
@@ -6935,7 +6991,7 @@
       <c r="I547" s="2"/>
       <c r="J547" s="2"/>
     </row>
-    <row r="548" ht="15.75" customHeight="1">
+    <row r="548" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
       <c r="C548" s="2"/>
@@ -6947,7 +7003,7 @@
       <c r="I548" s="2"/>
       <c r="J548" s="2"/>
     </row>
-    <row r="549" ht="15.75" customHeight="1">
+    <row r="549" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
       <c r="C549" s="2"/>
@@ -6959,7 +7015,7 @@
       <c r="I549" s="2"/>
       <c r="J549" s="2"/>
     </row>
-    <row r="550" ht="15.75" customHeight="1">
+    <row r="550" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
       <c r="C550" s="2"/>
@@ -6971,7 +7027,7 @@
       <c r="I550" s="2"/>
       <c r="J550" s="2"/>
     </row>
-    <row r="551" ht="15.75" customHeight="1">
+    <row r="551" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
       <c r="C551" s="2"/>
@@ -6983,7 +7039,7 @@
       <c r="I551" s="2"/>
       <c r="J551" s="2"/>
     </row>
-    <row r="552" ht="15.75" customHeight="1">
+    <row r="552" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
       <c r="C552" s="2"/>
@@ -6995,7 +7051,7 @@
       <c r="I552" s="2"/>
       <c r="J552" s="2"/>
     </row>
-    <row r="553" ht="15.75" customHeight="1">
+    <row r="553" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
       <c r="C553" s="2"/>
@@ -7007,7 +7063,7 @@
       <c r="I553" s="2"/>
       <c r="J553" s="2"/>
     </row>
-    <row r="554" ht="15.75" customHeight="1">
+    <row r="554" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
       <c r="C554" s="2"/>
@@ -7019,7 +7075,7 @@
       <c r="I554" s="2"/>
       <c r="J554" s="2"/>
     </row>
-    <row r="555" ht="15.75" customHeight="1">
+    <row r="555" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
       <c r="C555" s="2"/>
@@ -7031,7 +7087,7 @@
       <c r="I555" s="2"/>
       <c r="J555" s="2"/>
     </row>
-    <row r="556" ht="15.75" customHeight="1">
+    <row r="556" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
       <c r="C556" s="2"/>
@@ -7043,7 +7099,7 @@
       <c r="I556" s="2"/>
       <c r="J556" s="2"/>
     </row>
-    <row r="557" ht="15.75" customHeight="1">
+    <row r="557" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
       <c r="C557" s="2"/>
@@ -7055,7 +7111,7 @@
       <c r="I557" s="2"/>
       <c r="J557" s="2"/>
     </row>
-    <row r="558" ht="15.75" customHeight="1">
+    <row r="558" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
       <c r="C558" s="2"/>
@@ -7067,7 +7123,7 @@
       <c r="I558" s="2"/>
       <c r="J558" s="2"/>
     </row>
-    <row r="559" ht="15.75" customHeight="1">
+    <row r="559" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
       <c r="C559" s="2"/>
@@ -7079,7 +7135,7 @@
       <c r="I559" s="2"/>
       <c r="J559" s="2"/>
     </row>
-    <row r="560" ht="15.75" customHeight="1">
+    <row r="560" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
       <c r="C560" s="2"/>
@@ -7091,7 +7147,7 @@
       <c r="I560" s="2"/>
       <c r="J560" s="2"/>
     </row>
-    <row r="561" ht="15.75" customHeight="1">
+    <row r="561" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
       <c r="C561" s="2"/>
@@ -7103,7 +7159,7 @@
       <c r="I561" s="2"/>
       <c r="J561" s="2"/>
     </row>
-    <row r="562" ht="15.75" customHeight="1">
+    <row r="562" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
       <c r="C562" s="2"/>
@@ -7115,7 +7171,7 @@
       <c r="I562" s="2"/>
       <c r="J562" s="2"/>
     </row>
-    <row r="563" ht="15.75" customHeight="1">
+    <row r="563" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
       <c r="C563" s="2"/>
@@ -7127,7 +7183,7 @@
       <c r="I563" s="2"/>
       <c r="J563" s="2"/>
     </row>
-    <row r="564" ht="15.75" customHeight="1">
+    <row r="564" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
       <c r="C564" s="2"/>
@@ -7139,7 +7195,7 @@
       <c r="I564" s="2"/>
       <c r="J564" s="2"/>
     </row>
-    <row r="565" ht="15.75" customHeight="1">
+    <row r="565" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
       <c r="C565" s="2"/>
@@ -7151,7 +7207,7 @@
       <c r="I565" s="2"/>
       <c r="J565" s="2"/>
     </row>
-    <row r="566" ht="15.75" customHeight="1">
+    <row r="566" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
       <c r="C566" s="2"/>
@@ -7163,7 +7219,7 @@
       <c r="I566" s="2"/>
       <c r="J566" s="2"/>
     </row>
-    <row r="567" ht="15.75" customHeight="1">
+    <row r="567" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
       <c r="C567" s="2"/>
@@ -7175,7 +7231,7 @@
       <c r="I567" s="2"/>
       <c r="J567" s="2"/>
     </row>
-    <row r="568" ht="15.75" customHeight="1">
+    <row r="568" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
       <c r="C568" s="2"/>
@@ -7187,7 +7243,7 @@
       <c r="I568" s="2"/>
       <c r="J568" s="2"/>
     </row>
-    <row r="569" ht="15.75" customHeight="1">
+    <row r="569" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
       <c r="C569" s="2"/>
@@ -7199,7 +7255,7 @@
       <c r="I569" s="2"/>
       <c r="J569" s="2"/>
     </row>
-    <row r="570" ht="15.75" customHeight="1">
+    <row r="570" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
       <c r="C570" s="2"/>
@@ -7211,7 +7267,7 @@
       <c r="I570" s="2"/>
       <c r="J570" s="2"/>
     </row>
-    <row r="571" ht="15.75" customHeight="1">
+    <row r="571" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
       <c r="C571" s="2"/>
@@ -7223,7 +7279,7 @@
       <c r="I571" s="2"/>
       <c r="J571" s="2"/>
     </row>
-    <row r="572" ht="15.75" customHeight="1">
+    <row r="572" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
       <c r="C572" s="2"/>
@@ -7235,7 +7291,7 @@
       <c r="I572" s="2"/>
       <c r="J572" s="2"/>
     </row>
-    <row r="573" ht="15.75" customHeight="1">
+    <row r="573" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
       <c r="C573" s="2"/>
@@ -7247,7 +7303,7 @@
       <c r="I573" s="2"/>
       <c r="J573" s="2"/>
     </row>
-    <row r="574" ht="15.75" customHeight="1">
+    <row r="574" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
       <c r="C574" s="2"/>
@@ -7259,7 +7315,7 @@
       <c r="I574" s="2"/>
       <c r="J574" s="2"/>
     </row>
-    <row r="575" ht="15.75" customHeight="1">
+    <row r="575" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
       <c r="C575" s="2"/>
@@ -7271,7 +7327,7 @@
       <c r="I575" s="2"/>
       <c r="J575" s="2"/>
     </row>
-    <row r="576" ht="15.75" customHeight="1">
+    <row r="576" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
       <c r="C576" s="2"/>
@@ -7283,7 +7339,7 @@
       <c r="I576" s="2"/>
       <c r="J576" s="2"/>
     </row>
-    <row r="577" ht="15.75" customHeight="1">
+    <row r="577" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
       <c r="C577" s="2"/>
@@ -7295,7 +7351,7 @@
       <c r="I577" s="2"/>
       <c r="J577" s="2"/>
     </row>
-    <row r="578" ht="15.75" customHeight="1">
+    <row r="578" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
       <c r="C578" s="2"/>
@@ -7307,7 +7363,7 @@
       <c r="I578" s="2"/>
       <c r="J578" s="2"/>
     </row>
-    <row r="579" ht="15.75" customHeight="1">
+    <row r="579" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
       <c r="C579" s="2"/>
@@ -7319,7 +7375,7 @@
       <c r="I579" s="2"/>
       <c r="J579" s="2"/>
     </row>
-    <row r="580" ht="15.75" customHeight="1">
+    <row r="580" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
       <c r="C580" s="2"/>
@@ -7331,7 +7387,7 @@
       <c r="I580" s="2"/>
       <c r="J580" s="2"/>
     </row>
-    <row r="581" ht="15.75" customHeight="1">
+    <row r="581" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
       <c r="C581" s="2"/>
@@ -7343,7 +7399,7 @@
       <c r="I581" s="2"/>
       <c r="J581" s="2"/>
     </row>
-    <row r="582" ht="15.75" customHeight="1">
+    <row r="582" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
       <c r="C582" s="2"/>
@@ -7355,7 +7411,7 @@
       <c r="I582" s="2"/>
       <c r="J582" s="2"/>
     </row>
-    <row r="583" ht="15.75" customHeight="1">
+    <row r="583" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
       <c r="C583" s="2"/>
@@ -7367,7 +7423,7 @@
       <c r="I583" s="2"/>
       <c r="J583" s="2"/>
     </row>
-    <row r="584" ht="15.75" customHeight="1">
+    <row r="584" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
       <c r="C584" s="2"/>
@@ -7379,7 +7435,7 @@
       <c r="I584" s="2"/>
       <c r="J584" s="2"/>
     </row>
-    <row r="585" ht="15.75" customHeight="1">
+    <row r="585" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
       <c r="C585" s="2"/>
@@ -7391,7 +7447,7 @@
       <c r="I585" s="2"/>
       <c r="J585" s="2"/>
     </row>
-    <row r="586" ht="15.75" customHeight="1">
+    <row r="586" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
       <c r="C586" s="2"/>
@@ -7403,7 +7459,7 @@
       <c r="I586" s="2"/>
       <c r="J586" s="2"/>
     </row>
-    <row r="587" ht="15.75" customHeight="1">
+    <row r="587" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
       <c r="C587" s="2"/>
@@ -7415,7 +7471,7 @@
       <c r="I587" s="2"/>
       <c r="J587" s="2"/>
     </row>
-    <row r="588" ht="15.75" customHeight="1">
+    <row r="588" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
       <c r="C588" s="2"/>
@@ -7427,7 +7483,7 @@
       <c r="I588" s="2"/>
       <c r="J588" s="2"/>
     </row>
-    <row r="589" ht="15.75" customHeight="1">
+    <row r="589" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
       <c r="C589" s="2"/>
@@ -7439,7 +7495,7 @@
       <c r="I589" s="2"/>
       <c r="J589" s="2"/>
     </row>
-    <row r="590" ht="15.75" customHeight="1">
+    <row r="590" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
       <c r="C590" s="2"/>
@@ -7451,7 +7507,7 @@
       <c r="I590" s="2"/>
       <c r="J590" s="2"/>
     </row>
-    <row r="591" ht="15.75" customHeight="1">
+    <row r="591" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
       <c r="C591" s="2"/>
@@ -7463,7 +7519,7 @@
       <c r="I591" s="2"/>
       <c r="J591" s="2"/>
     </row>
-    <row r="592" ht="15.75" customHeight="1">
+    <row r="592" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
       <c r="C592" s="2"/>
@@ -7475,7 +7531,7 @@
       <c r="I592" s="2"/>
       <c r="J592" s="2"/>
     </row>
-    <row r="593" ht="15.75" customHeight="1">
+    <row r="593" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
       <c r="C593" s="2"/>
@@ -7487,7 +7543,7 @@
       <c r="I593" s="2"/>
       <c r="J593" s="2"/>
     </row>
-    <row r="594" ht="15.75" customHeight="1">
+    <row r="594" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
       <c r="C594" s="2"/>
@@ -7499,7 +7555,7 @@
       <c r="I594" s="2"/>
       <c r="J594" s="2"/>
     </row>
-    <row r="595" ht="15.75" customHeight="1">
+    <row r="595" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
       <c r="C595" s="2"/>
@@ -7511,7 +7567,7 @@
       <c r="I595" s="2"/>
       <c r="J595" s="2"/>
     </row>
-    <row r="596" ht="15.75" customHeight="1">
+    <row r="596" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
       <c r="C596" s="2"/>
@@ -7523,7 +7579,7 @@
       <c r="I596" s="2"/>
       <c r="J596" s="2"/>
     </row>
-    <row r="597" ht="15.75" customHeight="1">
+    <row r="597" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
       <c r="C597" s="2"/>
@@ -7535,7 +7591,7 @@
       <c r="I597" s="2"/>
       <c r="J597" s="2"/>
     </row>
-    <row r="598" ht="15.75" customHeight="1">
+    <row r="598" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
       <c r="C598" s="2"/>
@@ -7547,7 +7603,7 @@
       <c r="I598" s="2"/>
       <c r="J598" s="2"/>
     </row>
-    <row r="599" ht="15.75" customHeight="1">
+    <row r="599" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
       <c r="C599" s="2"/>
@@ -7559,7 +7615,7 @@
       <c r="I599" s="2"/>
       <c r="J599" s="2"/>
     </row>
-    <row r="600" ht="15.75" customHeight="1">
+    <row r="600" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
       <c r="C600" s="2"/>
@@ -7571,7 +7627,7 @@
       <c r="I600" s="2"/>
       <c r="J600" s="2"/>
     </row>
-    <row r="601" ht="15.75" customHeight="1">
+    <row r="601" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
       <c r="C601" s="2"/>
@@ -7583,7 +7639,7 @@
       <c r="I601" s="2"/>
       <c r="J601" s="2"/>
     </row>
-    <row r="602" ht="15.75" customHeight="1">
+    <row r="602" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
       <c r="C602" s="2"/>
@@ -7595,7 +7651,7 @@
       <c r="I602" s="2"/>
       <c r="J602" s="2"/>
     </row>
-    <row r="603" ht="15.75" customHeight="1">
+    <row r="603" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
       <c r="C603" s="2"/>
@@ -7607,7 +7663,7 @@
       <c r="I603" s="2"/>
       <c r="J603" s="2"/>
     </row>
-    <row r="604" ht="15.75" customHeight="1">
+    <row r="604" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
       <c r="C604" s="2"/>
@@ -7619,7 +7675,7 @@
       <c r="I604" s="2"/>
       <c r="J604" s="2"/>
     </row>
-    <row r="605" ht="15.75" customHeight="1">
+    <row r="605" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
       <c r="C605" s="2"/>
@@ -7631,7 +7687,7 @@
       <c r="I605" s="2"/>
       <c r="J605" s="2"/>
     </row>
-    <row r="606" ht="15.75" customHeight="1">
+    <row r="606" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
       <c r="C606" s="2"/>
@@ -7643,7 +7699,7 @@
       <c r="I606" s="2"/>
       <c r="J606" s="2"/>
     </row>
-    <row r="607" ht="15.75" customHeight="1">
+    <row r="607" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
       <c r="C607" s="2"/>
@@ -7655,7 +7711,7 @@
       <c r="I607" s="2"/>
       <c r="J607" s="2"/>
     </row>
-    <row r="608" ht="15.75" customHeight="1">
+    <row r="608" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
       <c r="C608" s="2"/>
@@ -7667,7 +7723,7 @@
       <c r="I608" s="2"/>
       <c r="J608" s="2"/>
     </row>
-    <row r="609" ht="15.75" customHeight="1">
+    <row r="609" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
       <c r="C609" s="2"/>
@@ -7679,7 +7735,7 @@
       <c r="I609" s="2"/>
       <c r="J609" s="2"/>
     </row>
-    <row r="610" ht="15.75" customHeight="1">
+    <row r="610" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
       <c r="C610" s="2"/>
@@ -7691,7 +7747,7 @@
       <c r="I610" s="2"/>
       <c r="J610" s="2"/>
     </row>
-    <row r="611" ht="15.75" customHeight="1">
+    <row r="611" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
       <c r="C611" s="2"/>
@@ -7703,7 +7759,7 @@
       <c r="I611" s="2"/>
       <c r="J611" s="2"/>
     </row>
-    <row r="612" ht="15.75" customHeight="1">
+    <row r="612" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
       <c r="C612" s="2"/>
@@ -7715,7 +7771,7 @@
       <c r="I612" s="2"/>
       <c r="J612" s="2"/>
     </row>
-    <row r="613" ht="15.75" customHeight="1">
+    <row r="613" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
       <c r="C613" s="2"/>
@@ -7727,7 +7783,7 @@
       <c r="I613" s="2"/>
       <c r="J613" s="2"/>
     </row>
-    <row r="614" ht="15.75" customHeight="1">
+    <row r="614" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
       <c r="C614" s="2"/>
@@ -7739,7 +7795,7 @@
       <c r="I614" s="2"/>
       <c r="J614" s="2"/>
     </row>
-    <row r="615" ht="15.75" customHeight="1">
+    <row r="615" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
       <c r="C615" s="2"/>
@@ -7751,7 +7807,7 @@
       <c r="I615" s="2"/>
       <c r="J615" s="2"/>
     </row>
-    <row r="616" ht="15.75" customHeight="1">
+    <row r="616" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
       <c r="C616" s="2"/>
@@ -7763,7 +7819,7 @@
       <c r="I616" s="2"/>
       <c r="J616" s="2"/>
     </row>
-    <row r="617" ht="15.75" customHeight="1">
+    <row r="617" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
       <c r="C617" s="2"/>
@@ -7775,7 +7831,7 @@
       <c r="I617" s="2"/>
       <c r="J617" s="2"/>
     </row>
-    <row r="618" ht="15.75" customHeight="1">
+    <row r="618" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
       <c r="C618" s="2"/>
@@ -7787,7 +7843,7 @@
       <c r="I618" s="2"/>
       <c r="J618" s="2"/>
     </row>
-    <row r="619" ht="15.75" customHeight="1">
+    <row r="619" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
       <c r="C619" s="2"/>
@@ -7799,7 +7855,7 @@
       <c r="I619" s="2"/>
       <c r="J619" s="2"/>
     </row>
-    <row r="620" ht="15.75" customHeight="1">
+    <row r="620" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
       <c r="C620" s="2"/>
@@ -7811,7 +7867,7 @@
       <c r="I620" s="2"/>
       <c r="J620" s="2"/>
     </row>
-    <row r="621" ht="15.75" customHeight="1">
+    <row r="621" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
       <c r="C621" s="2"/>
@@ -7823,7 +7879,7 @@
       <c r="I621" s="2"/>
       <c r="J621" s="2"/>
     </row>
-    <row r="622" ht="15.75" customHeight="1">
+    <row r="622" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
       <c r="C622" s="2"/>
@@ -7835,7 +7891,7 @@
       <c r="I622" s="2"/>
       <c r="J622" s="2"/>
     </row>
-    <row r="623" ht="15.75" customHeight="1">
+    <row r="623" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
       <c r="C623" s="2"/>
@@ -7847,7 +7903,7 @@
       <c r="I623" s="2"/>
       <c r="J623" s="2"/>
     </row>
-    <row r="624" ht="15.75" customHeight="1">
+    <row r="624" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
       <c r="C624" s="2"/>
@@ -7859,7 +7915,7 @@
       <c r="I624" s="2"/>
       <c r="J624" s="2"/>
     </row>
-    <row r="625" ht="15.75" customHeight="1">
+    <row r="625" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
       <c r="C625" s="2"/>
@@ -7871,7 +7927,7 @@
       <c r="I625" s="2"/>
       <c r="J625" s="2"/>
     </row>
-    <row r="626" ht="15.75" customHeight="1">
+    <row r="626" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
       <c r="C626" s="2"/>
@@ -7883,7 +7939,7 @@
       <c r="I626" s="2"/>
       <c r="J626" s="2"/>
     </row>
-    <row r="627" ht="15.75" customHeight="1">
+    <row r="627" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
       <c r="C627" s="2"/>
@@ -7895,7 +7951,7 @@
       <c r="I627" s="2"/>
       <c r="J627" s="2"/>
     </row>
-    <row r="628" ht="15.75" customHeight="1">
+    <row r="628" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
       <c r="C628" s="2"/>
@@ -7907,7 +7963,7 @@
       <c r="I628" s="2"/>
       <c r="J628" s="2"/>
     </row>
-    <row r="629" ht="15.75" customHeight="1">
+    <row r="629" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
       <c r="C629" s="2"/>
@@ -7919,7 +7975,7 @@
       <c r="I629" s="2"/>
       <c r="J629" s="2"/>
     </row>
-    <row r="630" ht="15.75" customHeight="1">
+    <row r="630" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
       <c r="C630" s="2"/>
@@ -7931,7 +7987,7 @@
       <c r="I630" s="2"/>
       <c r="J630" s="2"/>
     </row>
-    <row r="631" ht="15.75" customHeight="1">
+    <row r="631" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
       <c r="C631" s="2"/>
@@ -7943,7 +7999,7 @@
       <c r="I631" s="2"/>
       <c r="J631" s="2"/>
     </row>
-    <row r="632" ht="15.75" customHeight="1">
+    <row r="632" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
       <c r="C632" s="2"/>
@@ -7955,7 +8011,7 @@
       <c r="I632" s="2"/>
       <c r="J632" s="2"/>
     </row>
-    <row r="633" ht="15.75" customHeight="1">
+    <row r="633" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
       <c r="C633" s="2"/>
@@ -7967,7 +8023,7 @@
       <c r="I633" s="2"/>
       <c r="J633" s="2"/>
     </row>
-    <row r="634" ht="15.75" customHeight="1">
+    <row r="634" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
       <c r="C634" s="2"/>
@@ -7979,7 +8035,7 @@
       <c r="I634" s="2"/>
       <c r="J634" s="2"/>
     </row>
-    <row r="635" ht="15.75" customHeight="1">
+    <row r="635" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
       <c r="C635" s="2"/>
@@ -7991,7 +8047,7 @@
       <c r="I635" s="2"/>
       <c r="J635" s="2"/>
     </row>
-    <row r="636" ht="15.75" customHeight="1">
+    <row r="636" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
       <c r="C636" s="2"/>
@@ -8003,7 +8059,7 @@
       <c r="I636" s="2"/>
       <c r="J636" s="2"/>
     </row>
-    <row r="637" ht="15.75" customHeight="1">
+    <row r="637" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
       <c r="C637" s="2"/>
@@ -8015,7 +8071,7 @@
       <c r="I637" s="2"/>
       <c r="J637" s="2"/>
     </row>
-    <row r="638" ht="15.75" customHeight="1">
+    <row r="638" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
       <c r="C638" s="2"/>
@@ -8027,7 +8083,7 @@
       <c r="I638" s="2"/>
       <c r="J638" s="2"/>
     </row>
-    <row r="639" ht="15.75" customHeight="1">
+    <row r="639" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
       <c r="C639" s="2"/>
@@ -8039,7 +8095,7 @@
       <c r="I639" s="2"/>
       <c r="J639" s="2"/>
     </row>
-    <row r="640" ht="15.75" customHeight="1">
+    <row r="640" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
       <c r="C640" s="2"/>
@@ -8051,7 +8107,7 @@
       <c r="I640" s="2"/>
       <c r="J640" s="2"/>
     </row>
-    <row r="641" ht="15.75" customHeight="1">
+    <row r="641" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
       <c r="C641" s="2"/>
@@ -8063,7 +8119,7 @@
       <c r="I641" s="2"/>
       <c r="J641" s="2"/>
     </row>
-    <row r="642" ht="15.75" customHeight="1">
+    <row r="642" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
       <c r="C642" s="2"/>
@@ -8075,7 +8131,7 @@
       <c r="I642" s="2"/>
       <c r="J642" s="2"/>
     </row>
-    <row r="643" ht="15.75" customHeight="1">
+    <row r="643" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
       <c r="C643" s="2"/>
@@ -8087,7 +8143,7 @@
       <c r="I643" s="2"/>
       <c r="J643" s="2"/>
     </row>
-    <row r="644" ht="15.75" customHeight="1">
+    <row r="644" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
       <c r="C644" s="2"/>
@@ -8099,7 +8155,7 @@
       <c r="I644" s="2"/>
       <c r="J644" s="2"/>
     </row>
-    <row r="645" ht="15.75" customHeight="1">
+    <row r="645" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
       <c r="C645" s="2"/>
@@ -8111,7 +8167,7 @@
       <c r="I645" s="2"/>
       <c r="J645" s="2"/>
     </row>
-    <row r="646" ht="15.75" customHeight="1">
+    <row r="646" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
       <c r="C646" s="2"/>
@@ -8123,7 +8179,7 @@
       <c r="I646" s="2"/>
       <c r="J646" s="2"/>
     </row>
-    <row r="647" ht="15.75" customHeight="1">
+    <row r="647" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
       <c r="C647" s="2"/>
@@ -8135,7 +8191,7 @@
       <c r="I647" s="2"/>
       <c r="J647" s="2"/>
     </row>
-    <row r="648" ht="15.75" customHeight="1">
+    <row r="648" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
       <c r="C648" s="2"/>
@@ -8147,7 +8203,7 @@
       <c r="I648" s="2"/>
       <c r="J648" s="2"/>
     </row>
-    <row r="649" ht="15.75" customHeight="1">
+    <row r="649" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
       <c r="C649" s="2"/>
@@ -8159,7 +8215,7 @@
       <c r="I649" s="2"/>
       <c r="J649" s="2"/>
     </row>
-    <row r="650" ht="15.75" customHeight="1">
+    <row r="650" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
       <c r="C650" s="2"/>
@@ -8171,7 +8227,7 @@
       <c r="I650" s="2"/>
       <c r="J650" s="2"/>
     </row>
-    <row r="651" ht="15.75" customHeight="1">
+    <row r="651" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
       <c r="C651" s="2"/>
@@ -8183,7 +8239,7 @@
       <c r="I651" s="2"/>
       <c r="J651" s="2"/>
     </row>
-    <row r="652" ht="15.75" customHeight="1">
+    <row r="652" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
       <c r="C652" s="2"/>
@@ -8195,7 +8251,7 @@
       <c r="I652" s="2"/>
       <c r="J652" s="2"/>
     </row>
-    <row r="653" ht="15.75" customHeight="1">
+    <row r="653" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
       <c r="C653" s="2"/>
@@ -8207,7 +8263,7 @@
       <c r="I653" s="2"/>
       <c r="J653" s="2"/>
     </row>
-    <row r="654" ht="15.75" customHeight="1">
+    <row r="654" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
       <c r="C654" s="2"/>
@@ -8219,7 +8275,7 @@
       <c r="I654" s="2"/>
       <c r="J654" s="2"/>
     </row>
-    <row r="655" ht="15.75" customHeight="1">
+    <row r="655" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
       <c r="C655" s="2"/>
@@ -8231,7 +8287,7 @@
       <c r="I655" s="2"/>
       <c r="J655" s="2"/>
     </row>
-    <row r="656" ht="15.75" customHeight="1">
+    <row r="656" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
       <c r="C656" s="2"/>
@@ -8243,7 +8299,7 @@
       <c r="I656" s="2"/>
       <c r="J656" s="2"/>
     </row>
-    <row r="657" ht="15.75" customHeight="1">
+    <row r="657" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
       <c r="C657" s="2"/>
@@ -8255,7 +8311,7 @@
       <c r="I657" s="2"/>
       <c r="J657" s="2"/>
     </row>
-    <row r="658" ht="15.75" customHeight="1">
+    <row r="658" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
       <c r="C658" s="2"/>
@@ -8267,7 +8323,7 @@
       <c r="I658" s="2"/>
       <c r="J658" s="2"/>
     </row>
-    <row r="659" ht="15.75" customHeight="1">
+    <row r="659" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
       <c r="C659" s="2"/>
@@ -8279,7 +8335,7 @@
       <c r="I659" s="2"/>
       <c r="J659" s="2"/>
     </row>
-    <row r="660" ht="15.75" customHeight="1">
+    <row r="660" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
       <c r="C660" s="2"/>
@@ -8291,7 +8347,7 @@
       <c r="I660" s="2"/>
       <c r="J660" s="2"/>
     </row>
-    <row r="661" ht="15.75" customHeight="1">
+    <row r="661" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
       <c r="C661" s="2"/>
@@ -8303,7 +8359,7 @@
       <c r="I661" s="2"/>
       <c r="J661" s="2"/>
     </row>
-    <row r="662" ht="15.75" customHeight="1">
+    <row r="662" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
       <c r="C662" s="2"/>
@@ -8315,7 +8371,7 @@
       <c r="I662" s="2"/>
       <c r="J662" s="2"/>
     </row>
-    <row r="663" ht="15.75" customHeight="1">
+    <row r="663" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
       <c r="C663" s="2"/>
@@ -8327,7 +8383,7 @@
       <c r="I663" s="2"/>
       <c r="J663" s="2"/>
     </row>
-    <row r="664" ht="15.75" customHeight="1">
+    <row r="664" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
       <c r="C664" s="2"/>
@@ -8339,7 +8395,7 @@
       <c r="I664" s="2"/>
       <c r="J664" s="2"/>
     </row>
-    <row r="665" ht="15.75" customHeight="1">
+    <row r="665" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
       <c r="C665" s="2"/>
@@ -8351,7 +8407,7 @@
       <c r="I665" s="2"/>
       <c r="J665" s="2"/>
     </row>
-    <row r="666" ht="15.75" customHeight="1">
+    <row r="666" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
       <c r="C666" s="2"/>
@@ -8363,7 +8419,7 @@
       <c r="I666" s="2"/>
       <c r="J666" s="2"/>
     </row>
-    <row r="667" ht="15.75" customHeight="1">
+    <row r="667" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
       <c r="C667" s="2"/>
@@ -8375,7 +8431,7 @@
       <c r="I667" s="2"/>
       <c r="J667" s="2"/>
     </row>
-    <row r="668" ht="15.75" customHeight="1">
+    <row r="668" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
       <c r="C668" s="2"/>
@@ -8387,7 +8443,7 @@
       <c r="I668" s="2"/>
       <c r="J668" s="2"/>
     </row>
-    <row r="669" ht="15.75" customHeight="1">
+    <row r="669" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
       <c r="C669" s="2"/>
@@ -8399,7 +8455,7 @@
       <c r="I669" s="2"/>
       <c r="J669" s="2"/>
     </row>
-    <row r="670" ht="15.75" customHeight="1">
+    <row r="670" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
       <c r="C670" s="2"/>
@@ -8411,7 +8467,7 @@
       <c r="I670" s="2"/>
       <c r="J670" s="2"/>
     </row>
-    <row r="671" ht="15.75" customHeight="1">
+    <row r="671" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
       <c r="C671" s="2"/>
@@ -8423,7 +8479,7 @@
       <c r="I671" s="2"/>
       <c r="J671" s="2"/>
     </row>
-    <row r="672" ht="15.75" customHeight="1">
+    <row r="672" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
       <c r="C672" s="2"/>
@@ -8435,7 +8491,7 @@
       <c r="I672" s="2"/>
       <c r="J672" s="2"/>
     </row>
-    <row r="673" ht="15.75" customHeight="1">
+    <row r="673" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
       <c r="C673" s="2"/>
@@ -8447,7 +8503,7 @@
       <c r="I673" s="2"/>
       <c r="J673" s="2"/>
     </row>
-    <row r="674" ht="15.75" customHeight="1">
+    <row r="674" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
       <c r="C674" s="2"/>
@@ -8459,7 +8515,7 @@
       <c r="I674" s="2"/>
       <c r="J674" s="2"/>
     </row>
-    <row r="675" ht="15.75" customHeight="1">
+    <row r="675" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
       <c r="C675" s="2"/>
@@ -8471,7 +8527,7 @@
       <c r="I675" s="2"/>
       <c r="J675" s="2"/>
     </row>
-    <row r="676" ht="15.75" customHeight="1">
+    <row r="676" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
       <c r="C676" s="2"/>
@@ -8483,7 +8539,7 @@
       <c r="I676" s="2"/>
       <c r="J676" s="2"/>
     </row>
-    <row r="677" ht="15.75" customHeight="1">
+    <row r="677" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
       <c r="C677" s="2"/>
@@ -8495,7 +8551,7 @@
       <c r="I677" s="2"/>
       <c r="J677" s="2"/>
     </row>
-    <row r="678" ht="15.75" customHeight="1">
+    <row r="678" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
       <c r="C678" s="2"/>
@@ -8507,7 +8563,7 @@
       <c r="I678" s="2"/>
       <c r="J678" s="2"/>
     </row>
-    <row r="679" ht="15.75" customHeight="1">
+    <row r="679" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
       <c r="C679" s="2"/>
@@ -8519,7 +8575,7 @@
       <c r="I679" s="2"/>
       <c r="J679" s="2"/>
     </row>
-    <row r="680" ht="15.75" customHeight="1">
+    <row r="680" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
       <c r="C680" s="2"/>
@@ -8531,7 +8587,7 @@
       <c r="I680" s="2"/>
       <c r="J680" s="2"/>
     </row>
-    <row r="681" ht="15.75" customHeight="1">
+    <row r="681" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
       <c r="C681" s="2"/>
@@ -8543,7 +8599,7 @@
       <c r="I681" s="2"/>
       <c r="J681" s="2"/>
     </row>
-    <row r="682" ht="15.75" customHeight="1">
+    <row r="682" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
       <c r="C682" s="2"/>
@@ -8555,7 +8611,7 @@
       <c r="I682" s="2"/>
       <c r="J682" s="2"/>
     </row>
-    <row r="683" ht="15.75" customHeight="1">
+    <row r="683" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
       <c r="C683" s="2"/>
@@ -8567,7 +8623,7 @@
       <c r="I683" s="2"/>
       <c r="J683" s="2"/>
     </row>
-    <row r="684" ht="15.75" customHeight="1">
+    <row r="684" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
       <c r="C684" s="2"/>
@@ -8579,7 +8635,7 @@
       <c r="I684" s="2"/>
       <c r="J684" s="2"/>
     </row>
-    <row r="685" ht="15.75" customHeight="1">
+    <row r="685" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
       <c r="C685" s="2"/>
@@ -8591,7 +8647,7 @@
       <c r="I685" s="2"/>
       <c r="J685" s="2"/>
     </row>
-    <row r="686" ht="15.75" customHeight="1">
+    <row r="686" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
       <c r="C686" s="2"/>
@@ -8603,7 +8659,7 @@
       <c r="I686" s="2"/>
       <c r="J686" s="2"/>
     </row>
-    <row r="687" ht="15.75" customHeight="1">
+    <row r="687" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
       <c r="C687" s="2"/>
@@ -8615,7 +8671,7 @@
       <c r="I687" s="2"/>
       <c r="J687" s="2"/>
     </row>
-    <row r="688" ht="15.75" customHeight="1">
+    <row r="688" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
       <c r="C688" s="2"/>
@@ -8627,7 +8683,7 @@
       <c r="I688" s="2"/>
       <c r="J688" s="2"/>
     </row>
-    <row r="689" ht="15.75" customHeight="1">
+    <row r="689" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
       <c r="C689" s="2"/>
@@ -8639,7 +8695,7 @@
       <c r="I689" s="2"/>
       <c r="J689" s="2"/>
     </row>
-    <row r="690" ht="15.75" customHeight="1">
+    <row r="690" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
       <c r="C690" s="2"/>
@@ -8651,7 +8707,7 @@
       <c r="I690" s="2"/>
       <c r="J690" s="2"/>
     </row>
-    <row r="691" ht="15.75" customHeight="1">
+    <row r="691" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
       <c r="C691" s="2"/>
@@ -8663,7 +8719,7 @@
       <c r="I691" s="2"/>
       <c r="J691" s="2"/>
     </row>
-    <row r="692" ht="15.75" customHeight="1">
+    <row r="692" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
       <c r="C692" s="2"/>
@@ -8675,7 +8731,7 @@
       <c r="I692" s="2"/>
       <c r="J692" s="2"/>
     </row>
-    <row r="693" ht="15.75" customHeight="1">
+    <row r="693" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
       <c r="C693" s="2"/>
@@ -8687,7 +8743,7 @@
       <c r="I693" s="2"/>
       <c r="J693" s="2"/>
     </row>
-    <row r="694" ht="15.75" customHeight="1">
+    <row r="694" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
       <c r="C694" s="2"/>
@@ -8699,7 +8755,7 @@
       <c r="I694" s="2"/>
       <c r="J694" s="2"/>
     </row>
-    <row r="695" ht="15.75" customHeight="1">
+    <row r="695" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
       <c r="C695" s="2"/>
@@ -8711,7 +8767,7 @@
       <c r="I695" s="2"/>
       <c r="J695" s="2"/>
     </row>
-    <row r="696" ht="15.75" customHeight="1">
+    <row r="696" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
       <c r="C696" s="2"/>
@@ -8723,7 +8779,7 @@
       <c r="I696" s="2"/>
       <c r="J696" s="2"/>
     </row>
-    <row r="697" ht="15.75" customHeight="1">
+    <row r="697" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
       <c r="C697" s="2"/>
@@ -8735,7 +8791,7 @@
       <c r="I697" s="2"/>
       <c r="J697" s="2"/>
     </row>
-    <row r="698" ht="15.75" customHeight="1">
+    <row r="698" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
       <c r="C698" s="2"/>
@@ -8747,7 +8803,7 @@
       <c r="I698" s="2"/>
       <c r="J698" s="2"/>
     </row>
-    <row r="699" ht="15.75" customHeight="1">
+    <row r="699" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
       <c r="C699" s="2"/>
@@ -8759,7 +8815,7 @@
       <c r="I699" s="2"/>
       <c r="J699" s="2"/>
     </row>
-    <row r="700" ht="15.75" customHeight="1">
+    <row r="700" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
       <c r="C700" s="2"/>
@@ -8771,7 +8827,7 @@
       <c r="I700" s="2"/>
       <c r="J700" s="2"/>
     </row>
-    <row r="701" ht="15.75" customHeight="1">
+    <row r="701" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
       <c r="C701" s="2"/>
@@ -8783,7 +8839,7 @@
       <c r="I701" s="2"/>
       <c r="J701" s="2"/>
     </row>
-    <row r="702" ht="15.75" customHeight="1">
+    <row r="702" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
       <c r="C702" s="2"/>
@@ -8795,7 +8851,7 @@
       <c r="I702" s="2"/>
       <c r="J702" s="2"/>
     </row>
-    <row r="703" ht="15.75" customHeight="1">
+    <row r="703" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
       <c r="C703" s="2"/>
@@ -8807,7 +8863,7 @@
       <c r="I703" s="2"/>
       <c r="J703" s="2"/>
     </row>
-    <row r="704" ht="15.75" customHeight="1">
+    <row r="704" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
       <c r="C704" s="2"/>
@@ -8819,7 +8875,7 @@
       <c r="I704" s="2"/>
       <c r="J704" s="2"/>
     </row>
-    <row r="705" ht="15.75" customHeight="1">
+    <row r="705" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
       <c r="C705" s="2"/>
@@ -8831,7 +8887,7 @@
       <c r="I705" s="2"/>
       <c r="J705" s="2"/>
     </row>
-    <row r="706" ht="15.75" customHeight="1">
+    <row r="706" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
       <c r="C706" s="2"/>
@@ -8843,7 +8899,7 @@
       <c r="I706" s="2"/>
       <c r="J706" s="2"/>
     </row>
-    <row r="707" ht="15.75" customHeight="1">
+    <row r="707" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
       <c r="C707" s="2"/>
@@ -8855,7 +8911,7 @@
       <c r="I707" s="2"/>
       <c r="J707" s="2"/>
     </row>
-    <row r="708" ht="15.75" customHeight="1">
+    <row r="708" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
       <c r="C708" s="2"/>
@@ -8867,7 +8923,7 @@
       <c r="I708" s="2"/>
       <c r="J708" s="2"/>
     </row>
-    <row r="709" ht="15.75" customHeight="1">
+    <row r="709" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
       <c r="C709" s="2"/>
@@ -8879,7 +8935,7 @@
       <c r="I709" s="2"/>
       <c r="J709" s="2"/>
     </row>
-    <row r="710" ht="15.75" customHeight="1">
+    <row r="710" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
       <c r="C710" s="2"/>
@@ -8891,7 +8947,7 @@
       <c r="I710" s="2"/>
       <c r="J710" s="2"/>
     </row>
-    <row r="711" ht="15.75" customHeight="1">
+    <row r="711" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
       <c r="C711" s="2"/>
@@ -8903,7 +8959,7 @@
       <c r="I711" s="2"/>
       <c r="J711" s="2"/>
     </row>
-    <row r="712" ht="15.75" customHeight="1">
+    <row r="712" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
       <c r="C712" s="2"/>
@@ -8915,7 +8971,7 @@
       <c r="I712" s="2"/>
       <c r="J712" s="2"/>
     </row>
-    <row r="713" ht="15.75" customHeight="1">
+    <row r="713" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
       <c r="C713" s="2"/>
@@ -8927,7 +8983,7 @@
       <c r="I713" s="2"/>
       <c r="J713" s="2"/>
     </row>
-    <row r="714" ht="15.75" customHeight="1">
+    <row r="714" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
       <c r="C714" s="2"/>
@@ -8939,7 +8995,7 @@
       <c r="I714" s="2"/>
       <c r="J714" s="2"/>
     </row>
-    <row r="715" ht="15.75" customHeight="1">
+    <row r="715" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
       <c r="C715" s="2"/>
@@ -8951,7 +9007,7 @@
       <c r="I715" s="2"/>
       <c r="J715" s="2"/>
     </row>
-    <row r="716" ht="15.75" customHeight="1">
+    <row r="716" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
       <c r="C716" s="2"/>
@@ -8963,7 +9019,7 @@
       <c r="I716" s="2"/>
       <c r="J716" s="2"/>
     </row>
-    <row r="717" ht="15.75" customHeight="1">
+    <row r="717" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
       <c r="C717" s="2"/>
@@ -8975,7 +9031,7 @@
       <c r="I717" s="2"/>
       <c r="J717" s="2"/>
     </row>
-    <row r="718" ht="15.75" customHeight="1">
+    <row r="718" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
       <c r="C718" s="2"/>
@@ -8987,7 +9043,7 @@
       <c r="I718" s="2"/>
       <c r="J718" s="2"/>
     </row>
-    <row r="719" ht="15.75" customHeight="1">
+    <row r="719" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
       <c r="C719" s="2"/>
@@ -8999,7 +9055,7 @@
       <c r="I719" s="2"/>
       <c r="J719" s="2"/>
     </row>
-    <row r="720" ht="15.75" customHeight="1">
+    <row r="720" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
       <c r="C720" s="2"/>
@@ -9011,7 +9067,7 @@
       <c r="I720" s="2"/>
       <c r="J720" s="2"/>
     </row>
-    <row r="721" ht="15.75" customHeight="1">
+    <row r="721" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
       <c r="C721" s="2"/>
@@ -9023,7 +9079,7 @@
       <c r="I721" s="2"/>
       <c r="J721" s="2"/>
     </row>
-    <row r="722" ht="15.75" customHeight="1">
+    <row r="722" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
       <c r="C722" s="2"/>
@@ -9035,7 +9091,7 @@
       <c r="I722" s="2"/>
       <c r="J722" s="2"/>
     </row>
-    <row r="723" ht="15.75" customHeight="1">
+    <row r="723" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
       <c r="C723" s="2"/>
@@ -9047,7 +9103,7 @@
       <c r="I723" s="2"/>
       <c r="J723" s="2"/>
     </row>
-    <row r="724" ht="15.75" customHeight="1">
+    <row r="724" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
       <c r="C724" s="2"/>
@@ -9059,7 +9115,7 @@
       <c r="I724" s="2"/>
       <c r="J724" s="2"/>
     </row>
-    <row r="725" ht="15.75" customHeight="1">
+    <row r="725" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
       <c r="C725" s="2"/>
@@ -9071,7 +9127,7 @@
       <c r="I725" s="2"/>
       <c r="J725" s="2"/>
     </row>
-    <row r="726" ht="15.75" customHeight="1">
+    <row r="726" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
       <c r="C726" s="2"/>
@@ -9083,7 +9139,7 @@
       <c r="I726" s="2"/>
       <c r="J726" s="2"/>
     </row>
-    <row r="727" ht="15.75" customHeight="1">
+    <row r="727" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
       <c r="C727" s="2"/>
@@ -9095,7 +9151,7 @@
       <c r="I727" s="2"/>
       <c r="J727" s="2"/>
     </row>
-    <row r="728" ht="15.75" customHeight="1">
+    <row r="728" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
       <c r="C728" s="2"/>
@@ -9107,7 +9163,7 @@
       <c r="I728" s="2"/>
       <c r="J728" s="2"/>
     </row>
-    <row r="729" ht="15.75" customHeight="1">
+    <row r="729" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
       <c r="C729" s="2"/>
@@ -9119,7 +9175,7 @@
       <c r="I729" s="2"/>
       <c r="J729" s="2"/>
     </row>
-    <row r="730" ht="15.75" customHeight="1">
+    <row r="730" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
       <c r="C730" s="2"/>
@@ -9131,7 +9187,7 @@
       <c r="I730" s="2"/>
       <c r="J730" s="2"/>
     </row>
-    <row r="731" ht="15.75" customHeight="1">
+    <row r="731" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
       <c r="C731" s="2"/>
@@ -9143,7 +9199,7 @@
       <c r="I731" s="2"/>
       <c r="J731" s="2"/>
     </row>
-    <row r="732" ht="15.75" customHeight="1">
+    <row r="732" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
       <c r="C732" s="2"/>
@@ -9155,7 +9211,7 @@
       <c r="I732" s="2"/>
       <c r="J732" s="2"/>
     </row>
-    <row r="733" ht="15.75" customHeight="1">
+    <row r="733" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
       <c r="C733" s="2"/>
@@ -9167,7 +9223,7 @@
       <c r="I733" s="2"/>
       <c r="J733" s="2"/>
     </row>
-    <row r="734" ht="15.75" customHeight="1">
+    <row r="734" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
       <c r="C734" s="2"/>
@@ -9179,7 +9235,7 @@
       <c r="I734" s="2"/>
       <c r="J734" s="2"/>
     </row>
-    <row r="735" ht="15.75" customHeight="1">
+    <row r="735" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
       <c r="C735" s="2"/>
@@ -9191,7 +9247,7 @@
       <c r="I735" s="2"/>
       <c r="J735" s="2"/>
     </row>
-    <row r="736" ht="15.75" customHeight="1">
+    <row r="736" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
       <c r="C736" s="2"/>
@@ -9203,7 +9259,7 @@
       <c r="I736" s="2"/>
       <c r="J736" s="2"/>
     </row>
-    <row r="737" ht="15.75" customHeight="1">
+    <row r="737" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
       <c r="C737" s="2"/>
@@ -9215,7 +9271,7 @@
       <c r="I737" s="2"/>
       <c r="J737" s="2"/>
     </row>
-    <row r="738" ht="15.75" customHeight="1">
+    <row r="738" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
       <c r="C738" s="2"/>
@@ -9227,7 +9283,7 @@
       <c r="I738" s="2"/>
       <c r="J738" s="2"/>
     </row>
-    <row r="739" ht="15.75" customHeight="1">
+    <row r="739" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
       <c r="C739" s="2"/>
@@ -9239,7 +9295,7 @@
       <c r="I739" s="2"/>
       <c r="J739" s="2"/>
     </row>
-    <row r="740" ht="15.75" customHeight="1">
+    <row r="740" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
       <c r="C740" s="2"/>
@@ -9251,7 +9307,7 @@
       <c r="I740" s="2"/>
       <c r="J740" s="2"/>
     </row>
-    <row r="741" ht="15.75" customHeight="1">
+    <row r="741" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
       <c r="C741" s="2"/>
@@ -9263,7 +9319,7 @@
       <c r="I741" s="2"/>
       <c r="J741" s="2"/>
     </row>
-    <row r="742" ht="15.75" customHeight="1">
+    <row r="742" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
       <c r="C742" s="2"/>
@@ -9275,7 +9331,7 @@
       <c r="I742" s="2"/>
       <c r="J742" s="2"/>
     </row>
-    <row r="743" ht="15.75" customHeight="1">
+    <row r="743" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
       <c r="C743" s="2"/>
@@ -9287,7 +9343,7 @@
       <c r="I743" s="2"/>
       <c r="J743" s="2"/>
     </row>
-    <row r="744" ht="15.75" customHeight="1">
+    <row r="744" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
       <c r="C744" s="2"/>
@@ -9299,7 +9355,7 @@
       <c r="I744" s="2"/>
       <c r="J744" s="2"/>
     </row>
-    <row r="745" ht="15.75" customHeight="1">
+    <row r="745" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
       <c r="C745" s="2"/>
@@ -9311,7 +9367,7 @@
       <c r="I745" s="2"/>
       <c r="J745" s="2"/>
     </row>
-    <row r="746" ht="15.75" customHeight="1">
+    <row r="746" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
       <c r="C746" s="2"/>
@@ -9323,7 +9379,7 @@
       <c r="I746" s="2"/>
       <c r="J746" s="2"/>
     </row>
-    <row r="747" ht="15.75" customHeight="1">
+    <row r="747" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
       <c r="C747" s="2"/>
@@ -9335,7 +9391,7 @@
       <c r="I747" s="2"/>
       <c r="J747" s="2"/>
     </row>
-    <row r="748" ht="15.75" customHeight="1">
+    <row r="748" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
       <c r="C748" s="2"/>
@@ -9347,7 +9403,7 @@
       <c r="I748" s="2"/>
       <c r="J748" s="2"/>
     </row>
-    <row r="749" ht="15.75" customHeight="1">
+    <row r="749" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
       <c r="C749" s="2"/>
@@ -9359,7 +9415,7 @@
       <c r="I749" s="2"/>
       <c r="J749" s="2"/>
     </row>
-    <row r="750" ht="15.75" customHeight="1">
+    <row r="750" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
       <c r="C750" s="2"/>
@@ -9371,7 +9427,7 @@
       <c r="I750" s="2"/>
       <c r="J750" s="2"/>
     </row>
-    <row r="751" ht="15.75" customHeight="1">
+    <row r="751" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
       <c r="C751" s="2"/>
@@ -9383,7 +9439,7 @@
       <c r="I751" s="2"/>
       <c r="J751" s="2"/>
     </row>
-    <row r="752" ht="15.75" customHeight="1">
+    <row r="752" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
       <c r="C752" s="2"/>
@@ -9395,7 +9451,7 @@
       <c r="I752" s="2"/>
       <c r="J752" s="2"/>
     </row>
-    <row r="753" ht="15.75" customHeight="1">
+    <row r="753" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
       <c r="C753" s="2"/>
@@ -9407,7 +9463,7 @@
       <c r="I753" s="2"/>
       <c r="J753" s="2"/>
     </row>
-    <row r="754" ht="15.75" customHeight="1">
+    <row r="754" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
       <c r="C754" s="2"/>
@@ -9419,7 +9475,7 @@
       <c r="I754" s="2"/>
       <c r="J754" s="2"/>
     </row>
-    <row r="755" ht="15.75" customHeight="1">
+    <row r="755" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
       <c r="C755" s="2"/>
@@ -9431,7 +9487,7 @@
       <c r="I755" s="2"/>
       <c r="J755" s="2"/>
     </row>
-    <row r="756" ht="15.75" customHeight="1">
+    <row r="756" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
       <c r="C756" s="2"/>
@@ -9443,7 +9499,7 @@
       <c r="I756" s="2"/>
       <c r="J756" s="2"/>
     </row>
-    <row r="757" ht="15.75" customHeight="1">
+    <row r="757" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
       <c r="C757" s="2"/>
@@ -9455,7 +9511,7 @@
       <c r="I757" s="2"/>
       <c r="J757" s="2"/>
     </row>
-    <row r="758" ht="15.75" customHeight="1">
+    <row r="758" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
       <c r="C758" s="2"/>
@@ -9467,7 +9523,7 @@
       <c r="I758" s="2"/>
       <c r="J758" s="2"/>
     </row>
-    <row r="759" ht="15.75" customHeight="1">
+    <row r="759" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
       <c r="C759" s="2"/>
@@ -9479,7 +9535,7 @@
       <c r="I759" s="2"/>
       <c r="J759" s="2"/>
     </row>
-    <row r="760" ht="15.75" customHeight="1">
+    <row r="760" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
       <c r="C760" s="2"/>
@@ -9491,7 +9547,7 @@
       <c r="I760" s="2"/>
       <c r="J760" s="2"/>
     </row>
-    <row r="761" ht="15.75" customHeight="1">
+    <row r="761" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
       <c r="C761" s="2"/>
@@ -9503,7 +9559,7 @@
       <c r="I761" s="2"/>
       <c r="J761" s="2"/>
     </row>
-    <row r="762" ht="15.75" customHeight="1">
+    <row r="762" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
       <c r="C762" s="2"/>
@@ -9515,7 +9571,7 @@
       <c r="I762" s="2"/>
       <c r="J762" s="2"/>
     </row>
-    <row r="763" ht="15.75" customHeight="1">
+    <row r="763" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
       <c r="C763" s="2"/>
@@ -9527,7 +9583,7 @@
       <c r="I763" s="2"/>
       <c r="J763" s="2"/>
     </row>
-    <row r="764" ht="15.75" customHeight="1">
+    <row r="764" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
       <c r="C764" s="2"/>
@@ -9539,7 +9595,7 @@
       <c r="I764" s="2"/>
       <c r="J764" s="2"/>
     </row>
-    <row r="765" ht="15.75" customHeight="1">
+    <row r="765" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
       <c r="C765" s="2"/>
@@ -9551,7 +9607,7 @@
       <c r="I765" s="2"/>
       <c r="J765" s="2"/>
     </row>
-    <row r="766" ht="15.75" customHeight="1">
+    <row r="766" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
       <c r="C766" s="2"/>
@@ -9563,7 +9619,7 @@
       <c r="I766" s="2"/>
       <c r="J766" s="2"/>
     </row>
-    <row r="767" ht="15.75" customHeight="1">
+    <row r="767" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
       <c r="C767" s="2"/>
@@ -9575,7 +9631,7 @@
       <c r="I767" s="2"/>
       <c r="J767" s="2"/>
     </row>
-    <row r="768" ht="15.75" customHeight="1">
+    <row r="768" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
       <c r="C768" s="2"/>
@@ -9587,7 +9643,7 @@
       <c r="I768" s="2"/>
       <c r="J768" s="2"/>
     </row>
-    <row r="769" ht="15.75" customHeight="1">
+    <row r="769" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
       <c r="C769" s="2"/>
@@ -9599,7 +9655,7 @@
       <c r="I769" s="2"/>
       <c r="J769" s="2"/>
     </row>
-    <row r="770" ht="15.75" customHeight="1">
+    <row r="770" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
       <c r="C770" s="2"/>
@@ -9611,7 +9667,7 @@
       <c r="I770" s="2"/>
       <c r="J770" s="2"/>
     </row>
-    <row r="771" ht="15.75" customHeight="1">
+    <row r="771" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
       <c r="C771" s="2"/>
@@ -9623,7 +9679,7 @@
       <c r="I771" s="2"/>
       <c r="J771" s="2"/>
     </row>
-    <row r="772" ht="15.75" customHeight="1">
+    <row r="772" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
       <c r="C772" s="2"/>
@@ -9635,7 +9691,7 @@
       <c r="I772" s="2"/>
       <c r="J772" s="2"/>
     </row>
-    <row r="773" ht="15.75" customHeight="1">
+    <row r="773" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
       <c r="C773" s="2"/>
@@ -9647,7 +9703,7 @@
       <c r="I773" s="2"/>
       <c r="J773" s="2"/>
     </row>
-    <row r="774" ht="15.75" customHeight="1">
+    <row r="774" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
       <c r="C774" s="2"/>
@@ -9659,7 +9715,7 @@
       <c r="I774" s="2"/>
       <c r="J774" s="2"/>
     </row>
-    <row r="775" ht="15.75" customHeight="1">
+    <row r="775" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
       <c r="C775" s="2"/>
@@ -9671,7 +9727,7 @@
       <c r="I775" s="2"/>
       <c r="J775" s="2"/>
     </row>
-    <row r="776" ht="15.75" customHeight="1">
+    <row r="776" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
       <c r="C776" s="2"/>
@@ -9683,7 +9739,7 @@
       <c r="I776" s="2"/>
       <c r="J776" s="2"/>
     </row>
-    <row r="777" ht="15.75" customHeight="1">
+    <row r="777" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
       <c r="C777" s="2"/>
@@ -9695,7 +9751,7 @@
       <c r="I777" s="2"/>
       <c r="J777" s="2"/>
     </row>
-    <row r="778" ht="15.75" customHeight="1">
+    <row r="778" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
       <c r="C778" s="2"/>
@@ -9707,7 +9763,7 @@
       <c r="I778" s="2"/>
       <c r="J778" s="2"/>
     </row>
-    <row r="779" ht="15.75" customHeight="1">
+    <row r="779" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
       <c r="C779" s="2"/>
@@ -9719,7 +9775,7 @@
       <c r="I779" s="2"/>
       <c r="J779" s="2"/>
     </row>
-    <row r="780" ht="15.75" customHeight="1">
+    <row r="780" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
       <c r="C780" s="2"/>
@@ -9731,7 +9787,7 @@
       <c r="I780" s="2"/>
       <c r="J780" s="2"/>
     </row>
-    <row r="781" ht="15.75" customHeight="1">
+    <row r="781" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
       <c r="C781" s="2"/>
@@ -9743,7 +9799,7 @@
       <c r="I781" s="2"/>
       <c r="J781" s="2"/>
     </row>
-    <row r="782" ht="15.75" customHeight="1">
+    <row r="782" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
       <c r="C782" s="2"/>
@@ -9755,7 +9811,7 @@
       <c r="I782" s="2"/>
       <c r="J782" s="2"/>
     </row>
-    <row r="783" ht="15.75" customHeight="1">
+    <row r="783" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
       <c r="C783" s="2"/>
@@ -9767,7 +9823,7 @@
       <c r="I783" s="2"/>
       <c r="J783" s="2"/>
     </row>
-    <row r="784" ht="15.75" customHeight="1">
+    <row r="784" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
       <c r="C784" s="2"/>
@@ -9779,7 +9835,7 @@
       <c r="I784" s="2"/>
       <c r="J784" s="2"/>
     </row>
-    <row r="785" ht="15.75" customHeight="1">
+    <row r="785" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
       <c r="C785" s="2"/>
@@ -9791,7 +9847,7 @@
       <c r="I785" s="2"/>
       <c r="J785" s="2"/>
     </row>
-    <row r="786" ht="15.75" customHeight="1">
+    <row r="786" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
       <c r="C786" s="2"/>
@@ -9803,7 +9859,7 @@
       <c r="I786" s="2"/>
       <c r="J786" s="2"/>
     </row>
-    <row r="787" ht="15.75" customHeight="1">
+    <row r="787" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
       <c r="C787" s="2"/>
@@ -9815,7 +9871,7 @@
       <c r="I787" s="2"/>
       <c r="J787" s="2"/>
     </row>
-    <row r="788" ht="15.75" customHeight="1">
+    <row r="788" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
       <c r="C788" s="2"/>
@@ -9827,7 +9883,7 @@
       <c r="I788" s="2"/>
       <c r="J788" s="2"/>
     </row>
-    <row r="789" ht="15.75" customHeight="1">
+    <row r="789" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
       <c r="C789" s="2"/>
@@ -9839,7 +9895,7 @@
       <c r="I789" s="2"/>
       <c r="J789" s="2"/>
     </row>
-    <row r="790" ht="15.75" customHeight="1">
+    <row r="790" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
       <c r="C790" s="2"/>
@@ -9851,7 +9907,7 @@
       <c r="I790" s="2"/>
       <c r="J790" s="2"/>
     </row>
-    <row r="791" ht="15.75" customHeight="1">
+    <row r="791" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
       <c r="C791" s="2"/>
@@ -9863,7 +9919,7 @@
       <c r="I791" s="2"/>
       <c r="J791" s="2"/>
     </row>
-    <row r="792" ht="15.75" customHeight="1">
+    <row r="792" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
       <c r="C792" s="2"/>
@@ -9875,7 +9931,7 @@
       <c r="I792" s="2"/>
       <c r="J792" s="2"/>
     </row>
-    <row r="793" ht="15.75" customHeight="1">
+    <row r="793" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
       <c r="C793" s="2"/>
@@ -9887,7 +9943,7 @@
       <c r="I793" s="2"/>
       <c r="J793" s="2"/>
     </row>
-    <row r="794" ht="15.75" customHeight="1">
+    <row r="794" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
       <c r="C794" s="2"/>
@@ -9899,7 +9955,7 @@
       <c r="I794" s="2"/>
       <c r="J794" s="2"/>
     </row>
-    <row r="795" ht="15.75" customHeight="1">
+    <row r="795" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
       <c r="C795" s="2"/>
@@ -9911,7 +9967,7 @@
       <c r="I795" s="2"/>
       <c r="J795" s="2"/>
     </row>
-    <row r="796" ht="15.75" customHeight="1">
+    <row r="796" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
       <c r="C796" s="2"/>
@@ -9923,7 +9979,7 @@
       <c r="I796" s="2"/>
       <c r="J796" s="2"/>
     </row>
-    <row r="797" ht="15.75" customHeight="1">
+    <row r="797" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
       <c r="C797" s="2"/>
@@ -9935,7 +9991,7 @@
       <c r="I797" s="2"/>
       <c r="J797" s="2"/>
     </row>
-    <row r="798" ht="15.75" customHeight="1">
+    <row r="798" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
       <c r="C798" s="2"/>
@@ -9947,7 +10003,7 @@
       <c r="I798" s="2"/>
       <c r="J798" s="2"/>
     </row>
-    <row r="799" ht="15.75" customHeight="1">
+    <row r="799" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
       <c r="C799" s="2"/>
@@ -9959,7 +10015,7 @@
       <c r="I799" s="2"/>
       <c r="J799" s="2"/>
     </row>
-    <row r="800" ht="15.75" customHeight="1">
+    <row r="800" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
       <c r="C800" s="2"/>
@@ -9971,7 +10027,7 @@
       <c r="I800" s="2"/>
       <c r="J800" s="2"/>
     </row>
-    <row r="801" ht="15.75" customHeight="1">
+    <row r="801" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
       <c r="C801" s="2"/>
@@ -9983,7 +10039,7 @@
       <c r="I801" s="2"/>
       <c r="J801" s="2"/>
     </row>
-    <row r="802" ht="15.75" customHeight="1">
+    <row r="802" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
       <c r="C802" s="2"/>
@@ -9995,7 +10051,7 @@
       <c r="I802" s="2"/>
       <c r="J802" s="2"/>
     </row>
-    <row r="803" ht="15.75" customHeight="1">
+    <row r="803" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
       <c r="C803" s="2"/>
@@ -10007,7 +10063,7 @@
       <c r="I803" s="2"/>
       <c r="J803" s="2"/>
     </row>
-    <row r="804" ht="15.75" customHeight="1">
+    <row r="804" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
       <c r="C804" s="2"/>
@@ -10019,7 +10075,7 @@
       <c r="I804" s="2"/>
       <c r="J804" s="2"/>
     </row>
-    <row r="805" ht="15.75" customHeight="1">
+    <row r="805" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
       <c r="C805" s="2"/>
@@ -10031,7 +10087,7 @@
       <c r="I805" s="2"/>
       <c r="J805" s="2"/>
     </row>
-    <row r="806" ht="15.75" customHeight="1">
+    <row r="806" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
       <c r="C806" s="2"/>
@@ -10043,7 +10099,7 @@
       <c r="I806" s="2"/>
       <c r="J806" s="2"/>
     </row>
-    <row r="807" ht="15.75" customHeight="1">
+    <row r="807" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
       <c r="C807" s="2"/>
@@ -10055,7 +10111,7 @@
       <c r="I807" s="2"/>
       <c r="J807" s="2"/>
     </row>
-    <row r="808" ht="15.75" customHeight="1">
+    <row r="808" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
       <c r="C808" s="2"/>
@@ -10067,7 +10123,7 @@
       <c r="I808" s="2"/>
       <c r="J808" s="2"/>
     </row>
-    <row r="809" ht="15.75" customHeight="1">
+    <row r="809" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
       <c r="C809" s="2"/>
@@ -10079,7 +10135,7 @@
       <c r="I809" s="2"/>
       <c r="J809" s="2"/>
     </row>
-    <row r="810" ht="15.75" customHeight="1">
+    <row r="810" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
       <c r="C810" s="2"/>
@@ -10091,7 +10147,7 @@
       <c r="I810" s="2"/>
       <c r="J810" s="2"/>
     </row>
-    <row r="811" ht="15.75" customHeight="1">
+    <row r="811" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
       <c r="C811" s="2"/>
@@ -10103,7 +10159,7 @@
       <c r="I811" s="2"/>
       <c r="J811" s="2"/>
     </row>
-    <row r="812" ht="15.75" customHeight="1">
+    <row r="812" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
       <c r="C812" s="2"/>
@@ -10115,7 +10171,7 @@
       <c r="I812" s="2"/>
       <c r="J812" s="2"/>
     </row>
-    <row r="813" ht="15.75" customHeight="1">
+    <row r="813" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
       <c r="C813" s="2"/>
@@ -10127,7 +10183,7 @@
       <c r="I813" s="2"/>
       <c r="J813" s="2"/>
     </row>
-    <row r="814" ht="15.75" customHeight="1">
+    <row r="814" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
       <c r="C814" s="2"/>
@@ -10139,7 +10195,7 @@
       <c r="I814" s="2"/>
       <c r="J814" s="2"/>
     </row>
-    <row r="815" ht="15.75" customHeight="1">
+    <row r="815" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
       <c r="C815" s="2"/>
@@ -10151,7 +10207,7 @@
       <c r="I815" s="2"/>
       <c r="J815" s="2"/>
     </row>
-    <row r="816" ht="15.75" customHeight="1">
+    <row r="816" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
       <c r="C816" s="2"/>
@@ -10163,7 +10219,7 @@
       <c r="I816" s="2"/>
       <c r="J816" s="2"/>
     </row>
-    <row r="817" ht="15.75" customHeight="1">
+    <row r="817" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
       <c r="C817" s="2"/>
@@ -10175,7 +10231,7 @@
       <c r="I817" s="2"/>
       <c r="J817" s="2"/>
     </row>
-    <row r="818" ht="15.75" customHeight="1">
+    <row r="818" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
       <c r="C818" s="2"/>
@@ -10187,7 +10243,7 @@
       <c r="I818" s="2"/>
       <c r="J818" s="2"/>
     </row>
-    <row r="819" ht="15.75" customHeight="1">
+    <row r="819" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
       <c r="C819" s="2"/>
@@ -10199,7 +10255,7 @@
       <c r="I819" s="2"/>
       <c r="J819" s="2"/>
     </row>
-    <row r="820" ht="15.75" customHeight="1">
+    <row r="820" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
       <c r="C820" s="2"/>
@@ -10211,7 +10267,7 @@
       <c r="I820" s="2"/>
       <c r="J820" s="2"/>
     </row>
-    <row r="821" ht="15.75" customHeight="1">
+    <row r="821" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
       <c r="C821" s="2"/>
@@ -10223,7 +10279,7 @@
       <c r="I821" s="2"/>
       <c r="J821" s="2"/>
     </row>
-    <row r="822" ht="15.75" customHeight="1">
+    <row r="822" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
       <c r="C822" s="2"/>
@@ -10235,7 +10291,7 @@
       <c r="I822" s="2"/>
       <c r="J822" s="2"/>
     </row>
-    <row r="823" ht="15.75" customHeight="1">
+    <row r="823" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
       <c r="C823" s="2"/>
@@ -10247,7 +10303,7 @@
       <c r="I823" s="2"/>
       <c r="J823" s="2"/>
     </row>
-    <row r="824" ht="15.75" customHeight="1">
+    <row r="824" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
       <c r="C824" s="2"/>
@@ -10259,7 +10315,7 @@
       <c r="I824" s="2"/>
       <c r="J824" s="2"/>
     </row>
-    <row r="825" ht="15.75" customHeight="1">
+    <row r="825" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
       <c r="C825" s="2"/>
@@ -10271,7 +10327,7 @@
       <c r="I825" s="2"/>
       <c r="J825" s="2"/>
     </row>
-    <row r="826" ht="15.75" customHeight="1">
+    <row r="826" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
       <c r="C826" s="2"/>
@@ -10283,7 +10339,7 @@
       <c r="I826" s="2"/>
       <c r="J826" s="2"/>
     </row>
-    <row r="827" ht="15.75" customHeight="1">
+    <row r="827" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
       <c r="C827" s="2"/>
@@ -10295,7 +10351,7 @@
       <c r="I827" s="2"/>
       <c r="J827" s="2"/>
     </row>
-    <row r="828" ht="15.75" customHeight="1">
+    <row r="828" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
       <c r="C828" s="2"/>
@@ -10307,7 +10363,7 @@
       <c r="I828" s="2"/>
       <c r="J828" s="2"/>
     </row>
-    <row r="829" ht="15.75" customHeight="1">
+    <row r="829" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
       <c r="C829" s="2"/>
@@ -10319,7 +10375,7 @@
       <c r="I829" s="2"/>
       <c r="J829" s="2"/>
     </row>
-    <row r="830" ht="15.75" customHeight="1">
+    <row r="830" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
       <c r="C830" s="2"/>
@@ -10331,7 +10387,7 @@
       <c r="I830" s="2"/>
       <c r="J830" s="2"/>
     </row>
-    <row r="831" ht="15.75" customHeight="1">
+    <row r="831" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
       <c r="C831" s="2"/>
@@ -10343,7 +10399,7 @@
       <c r="I831" s="2"/>
       <c r="J831" s="2"/>
     </row>
-    <row r="832" ht="15.75" customHeight="1">
+    <row r="832" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
       <c r="C832" s="2"/>
@@ -10355,7 +10411,7 @@
       <c r="I832" s="2"/>
       <c r="J832" s="2"/>
     </row>
-    <row r="833" ht="15.75" customHeight="1">
+    <row r="833" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
       <c r="C833" s="2"/>
@@ -10367,7 +10423,7 @@
       <c r="I833" s="2"/>
       <c r="J833" s="2"/>
     </row>
-    <row r="834" ht="15.75" customHeight="1">
+    <row r="834" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
       <c r="C834" s="2"/>
@@ -10379,7 +10435,7 @@
       <c r="I834" s="2"/>
       <c r="J834" s="2"/>
     </row>
-    <row r="835" ht="15.75" customHeight="1">
+    <row r="835" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
       <c r="C835" s="2"/>
@@ -10391,7 +10447,7 @@
       <c r="I835" s="2"/>
       <c r="J835" s="2"/>
     </row>
-    <row r="836" ht="15.75" customHeight="1">
+    <row r="836" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
       <c r="C836" s="2"/>
@@ -10403,7 +10459,7 @@
       <c r="I836" s="2"/>
       <c r="J836" s="2"/>
     </row>
-    <row r="837" ht="15.75" customHeight="1">
+    <row r="837" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
       <c r="C837" s="2"/>
@@ -10415,7 +10471,7 @@
       <c r="I837" s="2"/>
       <c r="J837" s="2"/>
     </row>
-    <row r="838" ht="15.75" customHeight="1">
+    <row r="838" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
       <c r="C838" s="2"/>
@@ -10427,7 +10483,7 @@
       <c r="I838" s="2"/>
       <c r="J838" s="2"/>
     </row>
-    <row r="839" ht="15.75" customHeight="1">
+    <row r="839" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
       <c r="C839" s="2"/>
@@ -10439,7 +10495,7 @@
       <c r="I839" s="2"/>
       <c r="J839" s="2"/>
     </row>
-    <row r="840" ht="15.75" customHeight="1">
+    <row r="840" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
       <c r="C840" s="2"/>
@@ -10451,7 +10507,7 @@
       <c r="I840" s="2"/>
       <c r="J840" s="2"/>
     </row>
-    <row r="841" ht="15.75" customHeight="1">
+    <row r="841" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
       <c r="C841" s="2"/>
@@ -10463,7 +10519,7 @@
       <c r="I841" s="2"/>
       <c r="J841" s="2"/>
     </row>
-    <row r="842" ht="15.75" customHeight="1">
+    <row r="842" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
       <c r="C842" s="2"/>
@@ -10475,7 +10531,7 @@
       <c r="I842" s="2"/>
       <c r="J842" s="2"/>
     </row>
-    <row r="843" ht="15.75" customHeight="1">
+    <row r="843" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
       <c r="C843" s="2"/>
@@ -10487,7 +10543,7 @@
       <c r="I843" s="2"/>
       <c r="J843" s="2"/>
     </row>
-    <row r="844" ht="15.75" customHeight="1">
+    <row r="844" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
       <c r="C844" s="2"/>
@@ -10499,7 +10555,7 @@
       <c r="I844" s="2"/>
       <c r="J844" s="2"/>
     </row>
-    <row r="845" ht="15.75" customHeight="1">
+    <row r="845" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
       <c r="C845" s="2"/>
@@ -10511,7 +10567,7 @@
       <c r="I845" s="2"/>
       <c r="J845" s="2"/>
     </row>
-    <row r="846" ht="15.75" customHeight="1">
+    <row r="846" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
       <c r="C846" s="2"/>
@@ -10523,7 +10579,7 @@
       <c r="I846" s="2"/>
       <c r="J846" s="2"/>
     </row>
-    <row r="847" ht="15.75" customHeight="1">
+    <row r="847" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
       <c r="C847" s="2"/>
@@ -10535,7 +10591,7 @@
       <c r="I847" s="2"/>
       <c r="J847" s="2"/>
     </row>
-    <row r="848" ht="15.75" customHeight="1">
+    <row r="848" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
       <c r="C848" s="2"/>
@@ -10547,7 +10603,7 @@
       <c r="I848" s="2"/>
       <c r="J848" s="2"/>
     </row>
-    <row r="849" ht="15.75" customHeight="1">
+    <row r="849" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
       <c r="C849" s="2"/>
@@ -10559,7 +10615,7 @@
       <c r="I849" s="2"/>
       <c r="J849" s="2"/>
     </row>
-    <row r="850" ht="15.75" customHeight="1">
+    <row r="850" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
       <c r="C850" s="2"/>
@@ -10571,7 +10627,7 @@
       <c r="I850" s="2"/>
       <c r="J850" s="2"/>
     </row>
-    <row r="851" ht="15.75" customHeight="1">
+    <row r="851" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
       <c r="C851" s="2"/>
@@ -10583,7 +10639,7 @@
       <c r="I851" s="2"/>
       <c r="J851" s="2"/>
     </row>
-    <row r="852" ht="15.75" customHeight="1">
+    <row r="852" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
       <c r="C852" s="2"/>
@@ -10595,7 +10651,7 @@
       <c r="I852" s="2"/>
       <c r="J852" s="2"/>
     </row>
-    <row r="853" ht="15.75" customHeight="1">
+    <row r="853" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
       <c r="C853" s="2"/>
@@ -10607,7 +10663,7 @@
       <c r="I853" s="2"/>
       <c r="J853" s="2"/>
     </row>
-    <row r="854" ht="15.75" customHeight="1">
+    <row r="854" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
       <c r="C854" s="2"/>
@@ -10619,7 +10675,7 @@
       <c r="I854" s="2"/>
       <c r="J854" s="2"/>
     </row>
-    <row r="855" ht="15.75" customHeight="1">
+    <row r="855" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
       <c r="C855" s="2"/>
@@ -10631,7 +10687,7 @@
       <c r="I855" s="2"/>
       <c r="J855" s="2"/>
     </row>
-    <row r="856" ht="15.75" customHeight="1">
+    <row r="856" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
       <c r="C856" s="2"/>
@@ -10643,7 +10699,7 @@
       <c r="I856" s="2"/>
       <c r="J856" s="2"/>
     </row>
-    <row r="857" ht="15.75" customHeight="1">
+    <row r="857" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
       <c r="C857" s="2"/>
@@ -10655,7 +10711,7 @@
       <c r="I857" s="2"/>
       <c r="J857" s="2"/>
     </row>
-    <row r="858" ht="15.75" customHeight="1">
+    <row r="858" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
       <c r="C858" s="2"/>
@@ -10667,7 +10723,7 @@
       <c r="I858" s="2"/>
       <c r="J858" s="2"/>
     </row>
-    <row r="859" ht="15.75" customHeight="1">
+    <row r="859" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
       <c r="C859" s="2"/>
@@ -10679,7 +10735,7 @@
       <c r="I859" s="2"/>
       <c r="J859" s="2"/>
     </row>
-    <row r="860" ht="15.75" customHeight="1">
+    <row r="860" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
       <c r="C860" s="2"/>
@@ -10691,7 +10747,7 @@
       <c r="I860" s="2"/>
       <c r="J860" s="2"/>
     </row>
-    <row r="861" ht="15.75" customHeight="1">
+    <row r="861" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
       <c r="C861" s="2"/>
@@ -10703,7 +10759,7 @@
       <c r="I861" s="2"/>
       <c r="J861" s="2"/>
     </row>
-    <row r="862" ht="15.75" customHeight="1">
+    <row r="862" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
       <c r="C862" s="2"/>
@@ -10715,7 +10771,7 @@
       <c r="I862" s="2"/>
       <c r="J862" s="2"/>
     </row>
-    <row r="863" ht="15.75" customHeight="1">
+    <row r="863" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
       <c r="C863" s="2"/>
@@ -10727,7 +10783,7 @@
       <c r="I863" s="2"/>
       <c r="J863" s="2"/>
     </row>
-    <row r="864" ht="15.75" customHeight="1">
+    <row r="864" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
       <c r="C864" s="2"/>
@@ -10739,7 +10795,7 @@
       <c r="I864" s="2"/>
       <c r="J864" s="2"/>
     </row>
-    <row r="865" ht="15.75" customHeight="1">
+    <row r="865" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
       <c r="C865" s="2"/>
@@ -10751,7 +10807,7 @@
       <c r="I865" s="2"/>
       <c r="J865" s="2"/>
     </row>
-    <row r="866" ht="15.75" customHeight="1">
+    <row r="866" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
       <c r="C866" s="2"/>
@@ -10763,7 +10819,7 @@
       <c r="I866" s="2"/>
       <c r="J866" s="2"/>
     </row>
-    <row r="867" ht="15.75" customHeight="1">
+    <row r="867" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
       <c r="C867" s="2"/>
@@ -10775,7 +10831,7 @@
       <c r="I867" s="2"/>
       <c r="J867" s="2"/>
     </row>
-    <row r="868" ht="15.75" customHeight="1">
+    <row r="868" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
       <c r="C868" s="2"/>
@@ -10787,7 +10843,7 @@
       <c r="I868" s="2"/>
       <c r="J868" s="2"/>
     </row>
-    <row r="869" ht="15.75" customHeight="1">
+    <row r="869" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
       <c r="C869" s="2"/>
@@ -10799,7 +10855,7 @@
       <c r="I869" s="2"/>
       <c r="J869" s="2"/>
     </row>
-    <row r="870" ht="15.75" customHeight="1">
+    <row r="870" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
       <c r="C870" s="2"/>
@@ -10811,7 +10867,7 @@
       <c r="I870" s="2"/>
       <c r="J870" s="2"/>
     </row>
-    <row r="871" ht="15.75" customHeight="1">
+    <row r="871" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
       <c r="C871" s="2"/>
@@ -10823,7 +10879,7 @@
       <c r="I871" s="2"/>
       <c r="J871" s="2"/>
     </row>
-    <row r="872" ht="15.75" customHeight="1">
+    <row r="872" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
       <c r="C872" s="2"/>
@@ -10835,7 +10891,7 @@
       <c r="I872" s="2"/>
       <c r="J872" s="2"/>
     </row>
-    <row r="873" ht="15.75" customHeight="1">
+    <row r="873" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
       <c r="C873" s="2"/>
@@ -10847,7 +10903,7 @@
       <c r="I873" s="2"/>
       <c r="J873" s="2"/>
     </row>
-    <row r="874" ht="15.75" customHeight="1">
+    <row r="874" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
       <c r="C874" s="2"/>
@@ -10859,7 +10915,7 @@
       <c r="I874" s="2"/>
       <c r="J874" s="2"/>
     </row>
-    <row r="875" ht="15.75" customHeight="1">
+    <row r="875" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
       <c r="C875" s="2"/>
@@ -10871,7 +10927,7 @@
       <c r="I875" s="2"/>
       <c r="J875" s="2"/>
     </row>
-    <row r="876" ht="15.75" customHeight="1">
+    <row r="876" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
       <c r="C876" s="2"/>
@@ -10883,7 +10939,7 @@
       <c r="I876" s="2"/>
       <c r="J876" s="2"/>
     </row>
-    <row r="877" ht="15.75" customHeight="1">
+    <row r="877" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
       <c r="C877" s="2"/>
@@ -10895,7 +10951,7 @@
       <c r="I877" s="2"/>
       <c r="J877" s="2"/>
     </row>
-    <row r="878" ht="15.75" customHeight="1">
+    <row r="878" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
       <c r="C878" s="2"/>
@@ -10907,7 +10963,7 @@
       <c r="I878" s="2"/>
       <c r="J878" s="2"/>
     </row>
-    <row r="879" ht="15.75" customHeight="1">
+    <row r="879" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
       <c r="C879" s="2"/>
@@ -10919,7 +10975,7 @@
       <c r="I879" s="2"/>
       <c r="J879" s="2"/>
     </row>
-    <row r="880" ht="15.75" customHeight="1">
+    <row r="880" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
       <c r="C880" s="2"/>
@@ -10931,7 +10987,7 @@
       <c r="I880" s="2"/>
       <c r="J880" s="2"/>
     </row>
-    <row r="881" ht="15.75" customHeight="1">
+    <row r="881" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
       <c r="C881" s="2"/>
@@ -10943,7 +10999,7 @@
       <c r="I881" s="2"/>
       <c r="J881" s="2"/>
     </row>
-    <row r="882" ht="15.75" customHeight="1">
+    <row r="882" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
       <c r="C882" s="2"/>
@@ -10955,7 +11011,7 @@
       <c r="I882" s="2"/>
       <c r="J882" s="2"/>
     </row>
-    <row r="883" ht="15.75" customHeight="1">
+    <row r="883" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
       <c r="C883" s="2"/>
@@ -10967,7 +11023,7 @@
       <c r="I883" s="2"/>
       <c r="J883" s="2"/>
     </row>
-    <row r="884" ht="15.75" customHeight="1">
+    <row r="884" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
       <c r="C884" s="2"/>
@@ -10979,7 +11035,7 @@
       <c r="I884" s="2"/>
       <c r="J884" s="2"/>
     </row>
-    <row r="885" ht="15.75" customHeight="1">
+    <row r="885" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
       <c r="C885" s="2"/>
@@ -10991,7 +11047,7 @@
       <c r="I885" s="2"/>
       <c r="J885" s="2"/>
     </row>
-    <row r="886" ht="15.75" customHeight="1">
+    <row r="886" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
       <c r="C886" s="2"/>
@@ -11003,7 +11059,7 @@
       <c r="I886" s="2"/>
       <c r="J886" s="2"/>
     </row>
-    <row r="887" ht="15.75" customHeight="1">
+    <row r="887" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
       <c r="C887" s="2"/>
@@ -11015,7 +11071,7 @@
       <c r="I887" s="2"/>
       <c r="J887" s="2"/>
     </row>
-    <row r="888" ht="15.75" customHeight="1">
+    <row r="888" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
       <c r="C888" s="2"/>
@@ -11027,7 +11083,7 @@
       <c r="I888" s="2"/>
       <c r="J888" s="2"/>
     </row>
-    <row r="889" ht="15.75" customHeight="1">
+    <row r="889" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
       <c r="C889" s="2"/>
@@ -11039,7 +11095,7 @@
       <c r="I889" s="2"/>
       <c r="J889" s="2"/>
     </row>
-    <row r="890" ht="15.75" customHeight="1">
+    <row r="890" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
       <c r="C890" s="2"/>
@@ -11051,7 +11107,7 @@
       <c r="I890" s="2"/>
       <c r="J890" s="2"/>
     </row>
-    <row r="891" ht="15.75" customHeight="1">
+    <row r="891" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
       <c r="C891" s="2"/>
@@ -11063,7 +11119,7 @@
       <c r="I891" s="2"/>
       <c r="J891" s="2"/>
     </row>
-    <row r="892" ht="15.75" customHeight="1">
+    <row r="892" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
       <c r="C892" s="2"/>
@@ -11075,7 +11131,7 @@
       <c r="I892" s="2"/>
       <c r="J892" s="2"/>
     </row>
-    <row r="893" ht="15.75" customHeight="1">
+    <row r="893" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
       <c r="C893" s="2"/>
@@ -11087,7 +11143,7 @@
       <c r="I893" s="2"/>
       <c r="J893" s="2"/>
     </row>
-    <row r="894" ht="15.75" customHeight="1">
+    <row r="894" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
       <c r="C894" s="2"/>
@@ -11099,7 +11155,7 @@
       <c r="I894" s="2"/>
       <c r="J894" s="2"/>
     </row>
-    <row r="895" ht="15.75" customHeight="1">
+    <row r="895" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
       <c r="C895" s="2"/>
@@ -11111,7 +11167,7 @@
       <c r="I895" s="2"/>
       <c r="J895" s="2"/>
     </row>
-    <row r="896" ht="15.75" customHeight="1">
+    <row r="896" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
       <c r="C896" s="2"/>
@@ -11123,7 +11179,7 @@
       <c r="I896" s="2"/>
       <c r="J896" s="2"/>
     </row>
-    <row r="897" ht="15.75" customHeight="1">
+    <row r="897" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
       <c r="C897" s="2"/>
@@ -11135,7 +11191,7 @@
       <c r="I897" s="2"/>
       <c r="J897" s="2"/>
     </row>
-    <row r="898" ht="15.75" customHeight="1">
+    <row r="898" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
       <c r="C898" s="2"/>
@@ -11147,7 +11203,7 @@
       <c r="I898" s="2"/>
       <c r="J898" s="2"/>
     </row>
-    <row r="899" ht="15.75" customHeight="1">
+    <row r="899" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
       <c r="C899" s="2"/>
@@ -11159,7 +11215,7 @@
       <c r="I899" s="2"/>
       <c r="J899" s="2"/>
     </row>
-    <row r="900" ht="15.75" customHeight="1">
+    <row r="900" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
       <c r="C900" s="2"/>
@@ -11171,7 +11227,7 @@
       <c r="I900" s="2"/>
       <c r="J900" s="2"/>
     </row>
-    <row r="901" ht="15.75" customHeight="1">
+    <row r="901" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
       <c r="C901" s="2"/>
@@ -11183,7 +11239,7 @@
       <c r="I901" s="2"/>
       <c r="J901" s="2"/>
     </row>
-    <row r="902" ht="15.75" customHeight="1">
+    <row r="902" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
       <c r="C902" s="2"/>
@@ -11195,7 +11251,7 @@
       <c r="I902" s="2"/>
       <c r="J902" s="2"/>
     </row>
-    <row r="903" ht="15.75" customHeight="1">
+    <row r="903" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
       <c r="C903" s="2"/>
@@ -11207,7 +11263,7 @@
       <c r="I903" s="2"/>
       <c r="J903" s="2"/>
     </row>
-    <row r="904" ht="15.75" customHeight="1">
+    <row r="904" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
       <c r="C904" s="2"/>
@@ -11219,7 +11275,7 @@
       <c r="I904" s="2"/>
       <c r="J904" s="2"/>
     </row>
-    <row r="905" ht="15.75" customHeight="1">
+    <row r="905" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
       <c r="C905" s="2"/>
@@ -11231,7 +11287,7 @@
       <c r="I905" s="2"/>
       <c r="J905" s="2"/>
     </row>
-    <row r="906" ht="15.75" customHeight="1">
+    <row r="906" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
       <c r="C906" s="2"/>
@@ -11243,7 +11299,7 @@
       <c r="I906" s="2"/>
       <c r="J906" s="2"/>
     </row>
-    <row r="907" ht="15.75" customHeight="1">
+    <row r="907" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
       <c r="C907" s="2"/>
@@ -11255,7 +11311,7 @@
       <c r="I907" s="2"/>
       <c r="J907" s="2"/>
     </row>
-    <row r="908" ht="15.75" customHeight="1">
+    <row r="908" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
       <c r="C908" s="2"/>
@@ -11267,7 +11323,7 @@
       <c r="I908" s="2"/>
       <c r="J908" s="2"/>
     </row>
-    <row r="909" ht="15.75" customHeight="1">
+    <row r="909" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
       <c r="C909" s="2"/>
@@ -11279,7 +11335,7 @@
       <c r="I909" s="2"/>
       <c r="J909" s="2"/>
     </row>
-    <row r="910" ht="15.75" customHeight="1">
+    <row r="910" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
       <c r="C910" s="2"/>
@@ -11291,7 +11347,7 @@
       <c r="I910" s="2"/>
       <c r="J910" s="2"/>
     </row>
-    <row r="911" ht="15.75" customHeight="1">
+    <row r="911" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
       <c r="C911" s="2"/>
@@ -11303,7 +11359,7 @@
       <c r="I911" s="2"/>
       <c r="J911" s="2"/>
     </row>
-    <row r="912" ht="15.75" customHeight="1">
+    <row r="912" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
       <c r="C912" s="2"/>
@@ -11315,7 +11371,7 @@
       <c r="I912" s="2"/>
       <c r="J912" s="2"/>
     </row>
-    <row r="913" ht="15.75" customHeight="1">
+    <row r="913" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
       <c r="C913" s="2"/>
@@ -11327,7 +11383,7 @@
       <c r="I913" s="2"/>
       <c r="J913" s="2"/>
     </row>
-    <row r="914" ht="15.75" customHeight="1">
+    <row r="914" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
       <c r="C914" s="2"/>
@@ -11339,7 +11395,7 @@
       <c r="I914" s="2"/>
       <c r="J914" s="2"/>
     </row>
-    <row r="915" ht="15.75" customHeight="1">
+    <row r="915" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
       <c r="C915" s="2"/>
@@ -11351,7 +11407,7 @@
       <c r="I915" s="2"/>
       <c r="J915" s="2"/>
     </row>
-    <row r="916" ht="15.75" customHeight="1">
+    <row r="916" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
       <c r="C916" s="2"/>
@@ -11363,7 +11419,7 @@
       <c r="I916" s="2"/>
       <c r="J916" s="2"/>
     </row>
-    <row r="917" ht="15.75" customHeight="1">
+    <row r="917" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
       <c r="C917" s="2"/>
@@ -11375,7 +11431,7 @@
       <c r="I917" s="2"/>
       <c r="J917" s="2"/>
     </row>
-    <row r="918" ht="15.75" customHeight="1">
+    <row r="918" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
       <c r="C918" s="2"/>
@@ -11387,7 +11443,7 @@
       <c r="I918" s="2"/>
       <c r="J918" s="2"/>
     </row>
-    <row r="919" ht="15.75" customHeight="1">
+    <row r="919" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
       <c r="C919" s="2"/>
@@ -11399,7 +11455,7 @@
       <c r="I919" s="2"/>
       <c r="J919" s="2"/>
     </row>
-    <row r="920" ht="15.75" customHeight="1">
+    <row r="920" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
       <c r="C920" s="2"/>
@@ -11411,7 +11467,7 @@
       <c r="I920" s="2"/>
       <c r="J920" s="2"/>
     </row>
-    <row r="921" ht="15.75" customHeight="1">
+    <row r="921" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
       <c r="C921" s="2"/>
@@ -11423,7 +11479,7 @@
       <c r="I921" s="2"/>
       <c r="J921" s="2"/>
     </row>
-    <row r="922" ht="15.75" customHeight="1">
+    <row r="922" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
       <c r="C922" s="2"/>
@@ -11435,7 +11491,7 @@
       <c r="I922" s="2"/>
       <c r="J922" s="2"/>
     </row>
-    <row r="923" ht="15.75" customHeight="1">
+    <row r="923" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
       <c r="C923" s="2"/>
@@ -11447,7 +11503,7 @@
       <c r="I923" s="2"/>
       <c r="J923" s="2"/>
     </row>
-    <row r="924" ht="15.75" customHeight="1">
+    <row r="924" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
       <c r="C924" s="2"/>
@@ -11459,7 +11515,7 @@
       <c r="I924" s="2"/>
       <c r="J924" s="2"/>
     </row>
-    <row r="925" ht="15.75" customHeight="1">
+    <row r="925" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
       <c r="C925" s="2"/>
@@ -11471,7 +11527,7 @@
       <c r="I925" s="2"/>
       <c r="J925" s="2"/>
     </row>
-    <row r="926" ht="15.75" customHeight="1">
+    <row r="926" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
       <c r="C926" s="2"/>
@@ -11483,7 +11539,7 @@
       <c r="I926" s="2"/>
       <c r="J926" s="2"/>
     </row>
-    <row r="927" ht="15.75" customHeight="1">
+    <row r="927" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
       <c r="C927" s="2"/>
@@ -11495,7 +11551,7 @@
       <c r="I927" s="2"/>
       <c r="J927" s="2"/>
     </row>
-    <row r="928" ht="15.75" customHeight="1">
+    <row r="928" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
       <c r="C928" s="2"/>
@@ -11507,7 +11563,7 @@
       <c r="I928" s="2"/>
       <c r="J928" s="2"/>
     </row>
-    <row r="929" ht="15.75" customHeight="1">
+    <row r="929" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
       <c r="C929" s="2"/>
@@ -11519,7 +11575,7 @@
       <c r="I929" s="2"/>
       <c r="J929" s="2"/>
     </row>
-    <row r="930" ht="15.75" customHeight="1">
+    <row r="930" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
       <c r="C930" s="2"/>
@@ -11531,7 +11587,7 @@
       <c r="I930" s="2"/>
       <c r="J930" s="2"/>
     </row>
-    <row r="931" ht="15.75" customHeight="1">
+    <row r="931" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
       <c r="C931" s="2"/>
@@ -11543,7 +11599,7 @@
       <c r="I931" s="2"/>
       <c r="J931" s="2"/>
     </row>
-    <row r="932" ht="15.75" customHeight="1">
+    <row r="932" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
       <c r="C932" s="2"/>
@@ -11555,7 +11611,7 @@
       <c r="I932" s="2"/>
       <c r="J932" s="2"/>
     </row>
-    <row r="933" ht="15.75" customHeight="1">
+    <row r="933" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
       <c r="C933" s="2"/>
@@ -11567,7 +11623,7 @@
       <c r="I933" s="2"/>
       <c r="J933" s="2"/>
     </row>
-    <row r="934" ht="15.75" customHeight="1">
+    <row r="934" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
       <c r="C934" s="2"/>
@@ -11579,7 +11635,7 @@
       <c r="I934" s="2"/>
       <c r="J934" s="2"/>
     </row>
-    <row r="935" ht="15.75" customHeight="1">
+    <row r="935" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
       <c r="C935" s="2"/>
@@ -11591,7 +11647,7 @@
       <c r="I935" s="2"/>
       <c r="J935" s="2"/>
     </row>
-    <row r="936" ht="15.75" customHeight="1">
+    <row r="936" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
       <c r="C936" s="2"/>
@@ -11603,7 +11659,7 @@
       <c r="I936" s="2"/>
       <c r="J936" s="2"/>
     </row>
-    <row r="937" ht="15.75" customHeight="1">
+    <row r="937" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
       <c r="C937" s="2"/>
@@ -11615,7 +11671,7 @@
       <c r="I937" s="2"/>
       <c r="J937" s="2"/>
     </row>
-    <row r="938" ht="15.75" customHeight="1">
+    <row r="938" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
       <c r="C938" s="2"/>
@@ -11627,7 +11683,7 @@
       <c r="I938" s="2"/>
       <c r="J938" s="2"/>
     </row>
-    <row r="939" ht="15.75" customHeight="1">
+    <row r="939" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
       <c r="C939" s="2"/>
@@ -11639,7 +11695,7 @@
       <c r="I939" s="2"/>
       <c r="J939" s="2"/>
     </row>
-    <row r="940" ht="15.75" customHeight="1">
+    <row r="940" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
       <c r="C940" s="2"/>
@@ -11651,7 +11707,7 @@
       <c r="I940" s="2"/>
       <c r="J940" s="2"/>
     </row>
-    <row r="941" ht="15.75" customHeight="1">
+    <row r="941" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
       <c r="C941" s="2"/>
@@ -11663,7 +11719,7 @@
       <c r="I941" s="2"/>
       <c r="J941" s="2"/>
     </row>
-    <row r="942" ht="15.75" customHeight="1">
+    <row r="942" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A942" s="2"/>
       <c r="B942" s="2"/>
       <c r="C942" s="2"/>
@@ -11675,7 +11731,7 @@
       <c r="I942" s="2"/>
       <c r="J942" s="2"/>
     </row>
-    <row r="943" ht="15.75" customHeight="1">
+    <row r="943" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A943" s="2"/>
       <c r="B943" s="2"/>
       <c r="C943" s="2"/>
@@ -11687,7 +11743,7 @@
       <c r="I943" s="2"/>
       <c r="J943" s="2"/>
     </row>
-    <row r="944" ht="15.75" customHeight="1">
+    <row r="944" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A944" s="2"/>
       <c r="B944" s="2"/>
       <c r="C944" s="2"/>
@@ -11699,7 +11755,7 @@
       <c r="I944" s="2"/>
       <c r="J944" s="2"/>
     </row>
-    <row r="945" ht="15.75" customHeight="1">
+    <row r="945" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A945" s="2"/>
       <c r="B945" s="2"/>
       <c r="C945" s="2"/>
@@ -11711,7 +11767,7 @@
       <c r="I945" s="2"/>
       <c r="J945" s="2"/>
     </row>
-    <row r="946" ht="15.75" customHeight="1">
+    <row r="946" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A946" s="2"/>
       <c r="B946" s="2"/>
       <c r="C946" s="2"/>
@@ -11723,7 +11779,7 @@
       <c r="I946" s="2"/>
       <c r="J946" s="2"/>
     </row>
-    <row r="947" ht="15.75" customHeight="1">
+    <row r="947" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A947" s="2"/>
       <c r="B947" s="2"/>
       <c r="C947" s="2"/>
@@ -11735,7 +11791,7 @@
       <c r="I947" s="2"/>
       <c r="J947" s="2"/>
     </row>
-    <row r="948" ht="15.75" customHeight="1">
+    <row r="948" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A948" s="2"/>
       <c r="B948" s="2"/>
       <c r="C948" s="2"/>
@@ -11747,7 +11803,7 @@
       <c r="I948" s="2"/>
       <c r="J948" s="2"/>
     </row>
-    <row r="949" ht="15.75" customHeight="1">
+    <row r="949" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A949" s="2"/>
       <c r="B949" s="2"/>
       <c r="C949" s="2"/>
@@ -11759,7 +11815,7 @@
       <c r="I949" s="2"/>
       <c r="J949" s="2"/>
     </row>
-    <row r="950" ht="15.75" customHeight="1">
+    <row r="950" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A950" s="2"/>
       <c r="B950" s="2"/>
       <c r="C950" s="2"/>
@@ -11771,7 +11827,7 @@
       <c r="I950" s="2"/>
       <c r="J950" s="2"/>
     </row>
-    <row r="951" ht="15.75" customHeight="1">
+    <row r="951" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A951" s="2"/>
       <c r="B951" s="2"/>
       <c r="C951" s="2"/>
@@ -11783,7 +11839,7 @@
       <c r="I951" s="2"/>
       <c r="J951" s="2"/>
     </row>
-    <row r="952" ht="15.75" customHeight="1">
+    <row r="952" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A952" s="2"/>
       <c r="B952" s="2"/>
       <c r="C952" s="2"/>
@@ -11795,7 +11851,7 @@
       <c r="I952" s="2"/>
       <c r="J952" s="2"/>
     </row>
-    <row r="953" ht="15.75" customHeight="1">
+    <row r="953" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A953" s="2"/>
       <c r="B953" s="2"/>
       <c r="C953" s="2"/>
@@ -11807,7 +11863,7 @@
       <c r="I953" s="2"/>
       <c r="J953" s="2"/>
     </row>
-    <row r="954" ht="15.75" customHeight="1">
+    <row r="954" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A954" s="2"/>
       <c r="B954" s="2"/>
       <c r="C954" s="2"/>
@@ -11819,7 +11875,7 @@
       <c r="I954" s="2"/>
       <c r="J954" s="2"/>
     </row>
-    <row r="955" ht="15.75" customHeight="1">
+    <row r="955" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A955" s="2"/>
       <c r="B955" s="2"/>
       <c r="C955" s="2"/>
@@ -11831,7 +11887,7 @@
       <c r="I955" s="2"/>
       <c r="J955" s="2"/>
     </row>
-    <row r="956" ht="15.75" customHeight="1">
+    <row r="956" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A956" s="2"/>
       <c r="B956" s="2"/>
       <c r="C956" s="2"/>
@@ -11843,7 +11899,7 @@
       <c r="I956" s="2"/>
       <c r="J956" s="2"/>
     </row>
-    <row r="957" ht="15.75" customHeight="1">
+    <row r="957" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A957" s="2"/>
       <c r="B957" s="2"/>
       <c r="C957" s="2"/>
@@ -11855,7 +11911,7 @@
       <c r="I957" s="2"/>
       <c r="J957" s="2"/>
     </row>
-    <row r="958" ht="15.75" customHeight="1">
+    <row r="958" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A958" s="2"/>
       <c r="B958" s="2"/>
       <c r="C958" s="2"/>
@@ -11867,7 +11923,7 @@
       <c r="I958" s="2"/>
       <c r="J958" s="2"/>
     </row>
-    <row r="959" ht="15.75" customHeight="1">
+    <row r="959" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A959" s="2"/>
       <c r="B959" s="2"/>
       <c r="C959" s="2"/>
@@ -11879,7 +11935,7 @@
       <c r="I959" s="2"/>
       <c r="J959" s="2"/>
     </row>
-    <row r="960" ht="15.75" customHeight="1">
+    <row r="960" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A960" s="2"/>
       <c r="B960" s="2"/>
       <c r="C960" s="2"/>
@@ -11891,7 +11947,7 @@
       <c r="I960" s="2"/>
       <c r="J960" s="2"/>
     </row>
-    <row r="961" ht="15.75" customHeight="1">
+    <row r="961" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A961" s="2"/>
       <c r="B961" s="2"/>
       <c r="C961" s="2"/>
@@ -11903,7 +11959,7 @@
       <c r="I961" s="2"/>
       <c r="J961" s="2"/>
     </row>
-    <row r="962" ht="15.75" customHeight="1">
+    <row r="962" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A962" s="2"/>
       <c r="B962" s="2"/>
       <c r="C962" s="2"/>
@@ -11915,7 +11971,7 @@
       <c r="I962" s="2"/>
       <c r="J962" s="2"/>
     </row>
-    <row r="963" ht="15.75" customHeight="1">
+    <row r="963" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A963" s="2"/>
       <c r="B963" s="2"/>
       <c r="C963" s="2"/>
@@ -11927,7 +11983,7 @@
       <c r="I963" s="2"/>
       <c r="J963" s="2"/>
     </row>
-    <row r="964" ht="15.75" customHeight="1">
+    <row r="964" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A964" s="2"/>
       <c r="B964" s="2"/>
       <c r="C964" s="2"/>
@@ -11939,7 +11995,7 @@
       <c r="I964" s="2"/>
       <c r="J964" s="2"/>
     </row>
-    <row r="965" ht="15.75" customHeight="1">
+    <row r="965" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A965" s="2"/>
       <c r="B965" s="2"/>
       <c r="C965" s="2"/>
@@ -11951,7 +12007,7 @@
       <c r="I965" s="2"/>
       <c r="J965" s="2"/>
     </row>
-    <row r="966" ht="15.75" customHeight="1">
+    <row r="966" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A966" s="2"/>
       <c r="B966" s="2"/>
       <c r="C966" s="2"/>
@@ -11963,7 +12019,7 @@
       <c r="I966" s="2"/>
       <c r="J966" s="2"/>
     </row>
-    <row r="967" ht="15.75" customHeight="1">
+    <row r="967" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A967" s="2"/>
       <c r="B967" s="2"/>
       <c r="C967" s="2"/>
@@ -11975,7 +12031,7 @@
       <c r="I967" s="2"/>
       <c r="J967" s="2"/>
     </row>
-    <row r="968" ht="15.75" customHeight="1">
+    <row r="968" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A968" s="2"/>
       <c r="B968" s="2"/>
       <c r="C968" s="2"/>
@@ -11987,7 +12043,7 @@
       <c r="I968" s="2"/>
       <c r="J968" s="2"/>
     </row>
-    <row r="969" ht="15.75" customHeight="1">
+    <row r="969" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A969" s="2"/>
       <c r="B969" s="2"/>
       <c r="C969" s="2"/>
@@ -11999,7 +12055,7 @@
       <c r="I969" s="2"/>
       <c r="J969" s="2"/>
     </row>
-    <row r="970" ht="15.75" customHeight="1">
+    <row r="970" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A970" s="2"/>
       <c r="B970" s="2"/>
       <c r="C970" s="2"/>
@@ -12011,7 +12067,7 @@
       <c r="I970" s="2"/>
       <c r="J970" s="2"/>
     </row>
-    <row r="971" ht="15.75" customHeight="1">
+    <row r="971" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A971" s="2"/>
       <c r="B971" s="2"/>
       <c r="C971" s="2"/>
@@ -12023,7 +12079,7 @@
       <c r="I971" s="2"/>
       <c r="J971" s="2"/>
     </row>
-    <row r="972" ht="15.75" customHeight="1">
+    <row r="972" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A972" s="2"/>
       <c r="B972" s="2"/>
       <c r="C972" s="2"/>
@@ -12035,7 +12091,7 @@
       <c r="I972" s="2"/>
       <c r="J972" s="2"/>
     </row>
-    <row r="973" ht="15.75" customHeight="1">
+    <row r="973" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A973" s="2"/>
       <c r="B973" s="2"/>
       <c r="C973" s="2"/>
@@ -12047,7 +12103,7 @@
       <c r="I973" s="2"/>
       <c r="J973" s="2"/>
     </row>
-    <row r="974" ht="15.75" customHeight="1">
+    <row r="974" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A974" s="2"/>
       <c r="B974" s="2"/>
       <c r="C974" s="2"/>
@@ -12059,7 +12115,7 @@
       <c r="I974" s="2"/>
       <c r="J974" s="2"/>
     </row>
-    <row r="975" ht="15.75" customHeight="1">
+    <row r="975" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A975" s="2"/>
       <c r="B975" s="2"/>
       <c r="C975" s="2"/>
@@ -12071,7 +12127,7 @@
       <c r="I975" s="2"/>
       <c r="J975" s="2"/>
     </row>
-    <row r="976" ht="15.75" customHeight="1">
+    <row r="976" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A976" s="2"/>
       <c r="B976" s="2"/>
       <c r="C976" s="2"/>
@@ -12083,7 +12139,7 @@
       <c r="I976" s="2"/>
       <c r="J976" s="2"/>
     </row>
-    <row r="977" ht="15.75" customHeight="1">
+    <row r="977" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A977" s="2"/>
       <c r="B977" s="2"/>
       <c r="C977" s="2"/>
@@ -12095,7 +12151,7 @@
       <c r="I977" s="2"/>
       <c r="J977" s="2"/>
     </row>
-    <row r="978" ht="15.75" customHeight="1">
+    <row r="978" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A978" s="2"/>
       <c r="B978" s="2"/>
       <c r="C978" s="2"/>
@@ -12107,7 +12163,7 @@
       <c r="I978" s="2"/>
       <c r="J978" s="2"/>
     </row>
-    <row r="979" ht="15.75" customHeight="1">
+    <row r="979" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A979" s="2"/>
       <c r="B979" s="2"/>
       <c r="C979" s="2"/>
@@ -12119,7 +12175,7 @@
       <c r="I979" s="2"/>
       <c r="J979" s="2"/>
     </row>
-    <row r="980" ht="15.75" customHeight="1">
+    <row r="980" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A980" s="2"/>
       <c r="B980" s="2"/>
       <c r="C980" s="2"/>
@@ -12131,7 +12187,7 @@
       <c r="I980" s="2"/>
       <c r="J980" s="2"/>
     </row>
-    <row r="981" ht="15.75" customHeight="1">
+    <row r="981" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A981" s="2"/>
       <c r="B981" s="2"/>
       <c r="C981" s="2"/>
@@ -12143,7 +12199,7 @@
       <c r="I981" s="2"/>
       <c r="J981" s="2"/>
     </row>
-    <row r="982" ht="15.75" customHeight="1">
+    <row r="982" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A982" s="2"/>
       <c r="B982" s="2"/>
       <c r="C982" s="2"/>
@@ -12155,7 +12211,7 @@
       <c r="I982" s="2"/>
       <c r="J982" s="2"/>
     </row>
-    <row r="983" ht="15.75" customHeight="1">
+    <row r="983" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A983" s="2"/>
       <c r="B983" s="2"/>
       <c r="C983" s="2"/>
@@ -12167,7 +12223,7 @@
       <c r="I983" s="2"/>
       <c r="J983" s="2"/>
     </row>
-    <row r="984" ht="15.75" customHeight="1">
+    <row r="984" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A984" s="2"/>
       <c r="B984" s="2"/>
       <c r="C984" s="2"/>
@@ -12179,7 +12235,7 @@
       <c r="I984" s="2"/>
       <c r="J984" s="2"/>
     </row>
-    <row r="985" ht="15.75" customHeight="1">
+    <row r="985" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A985" s="2"/>
       <c r="B985" s="2"/>
       <c r="C985" s="2"/>
@@ -12191,7 +12247,7 @@
       <c r="I985" s="2"/>
       <c r="J985" s="2"/>
     </row>
-    <row r="986" ht="15.75" customHeight="1">
+    <row r="986" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A986" s="2"/>
       <c r="B986" s="2"/>
       <c r="C986" s="2"/>
@@ -12203,7 +12259,7 @@
       <c r="I986" s="2"/>
       <c r="J986" s="2"/>
     </row>
-    <row r="987" ht="15.75" customHeight="1">
+    <row r="987" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A987" s="2"/>
       <c r="B987" s="2"/>
       <c r="C987" s="2"/>
@@ -12215,7 +12271,7 @@
       <c r="I987" s="2"/>
       <c r="J987" s="2"/>
     </row>
-    <row r="988" ht="15.75" customHeight="1">
+    <row r="988" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A988" s="2"/>
       <c r="B988" s="2"/>
       <c r="C988" s="2"/>
@@ -12227,7 +12283,7 @@
       <c r="I988" s="2"/>
       <c r="J988" s="2"/>
     </row>
-    <row r="989" ht="15.75" customHeight="1">
+    <row r="989" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A989" s="2"/>
       <c r="B989" s="2"/>
       <c r="C989" s="2"/>
@@ -12239,7 +12295,7 @@
       <c r="I989" s="2"/>
       <c r="J989" s="2"/>
     </row>
-    <row r="990" ht="15.75" customHeight="1">
+    <row r="990" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A990" s="2"/>
       <c r="B990" s="2"/>
       <c r="C990" s="2"/>
@@ -12251,7 +12307,7 @@
       <c r="I990" s="2"/>
       <c r="J990" s="2"/>
     </row>
-    <row r="991" ht="15.75" customHeight="1">
+    <row r="991" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A991" s="2"/>
       <c r="B991" s="2"/>
       <c r="C991" s="2"/>
@@ -12263,7 +12319,7 @@
       <c r="I991" s="2"/>
       <c r="J991" s="2"/>
     </row>
-    <row r="992" ht="15.75" customHeight="1">
+    <row r="992" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A992" s="2"/>
       <c r="B992" s="2"/>
       <c r="C992" s="2"/>
@@ -12275,7 +12331,7 @@
       <c r="I992" s="2"/>
       <c r="J992" s="2"/>
     </row>
-    <row r="993" ht="15.75" customHeight="1">
+    <row r="993" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A993" s="2"/>
       <c r="B993" s="2"/>
       <c r="C993" s="2"/>
@@ -12287,7 +12343,7 @@
       <c r="I993" s="2"/>
       <c r="J993" s="2"/>
     </row>
-    <row r="994" ht="15.75" customHeight="1">
+    <row r="994" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A994" s="2"/>
       <c r="B994" s="2"/>
       <c r="C994" s="2"/>
@@ -12299,7 +12355,7 @@
       <c r="I994" s="2"/>
       <c r="J994" s="2"/>
     </row>
-    <row r="995" ht="15.75" customHeight="1">
+    <row r="995" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A995" s="2"/>
       <c r="B995" s="2"/>
       <c r="C995" s="2"/>
@@ -12311,7 +12367,7 @@
       <c r="I995" s="2"/>
       <c r="J995" s="2"/>
     </row>
-    <row r="996" ht="15.75" customHeight="1">
+    <row r="996" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A996" s="2"/>
       <c r="B996" s="2"/>
       <c r="C996" s="2"/>
@@ -12323,7 +12379,7 @@
       <c r="I996" s="2"/>
       <c r="J996" s="2"/>
     </row>
-    <row r="997" ht="15.75" customHeight="1">
+    <row r="997" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A997" s="2"/>
       <c r="B997" s="2"/>
       <c r="C997" s="2"/>
@@ -12335,7 +12391,7 @@
       <c r="I997" s="2"/>
       <c r="J997" s="2"/>
     </row>
-    <row r="998" ht="15.75" customHeight="1">
+    <row r="998" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A998" s="2"/>
       <c r="B998" s="2"/>
       <c r="C998" s="2"/>
@@ -12347,7 +12403,7 @@
       <c r="I998" s="2"/>
       <c r="J998" s="2"/>
     </row>
-    <row r="999" ht="15.75" customHeight="1">
+    <row r="999" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A999" s="2"/>
       <c r="B999" s="2"/>
       <c r="C999" s="2"/>
@@ -12359,7 +12415,7 @@
       <c r="I999" s="2"/>
       <c r="J999" s="2"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
+    <row r="1000" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1000" s="2"/>
       <c r="B1000" s="2"/>
       <c r="C1000" s="2"/>
@@ -12372,9 +12428,8 @@
       <c r="J1000" s="2"/>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>